--- a/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_3.xlsx
+++ b/streamlit_dashboard_monitoring/captured_data/with_ASCON/ppg_sensor_ascon_3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H154"/>
+  <dimension ref="A1:M145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,4595 +469,6510 @@
           <t>Sensor_Status</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>CPU_Load_%</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Memory_Used_%</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Latency_ms</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Enc_Time_us</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Dec_Time_ms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:20.738</t>
+          <t>2026-05-29 09:34:23.591</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1779421642473</v>
+        <v>1780022062176</v>
       </c>
       <c r="C2" t="n">
-        <v>89271</v>
+        <v>82988</v>
       </c>
       <c r="D2" t="n">
-        <v>76.66</v>
+        <v>151.44</v>
       </c>
       <c r="E2" t="n">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="F2" t="n">
-        <v>1631</v>
+        <v>1220</v>
       </c>
       <c r="G2" t="n">
-        <v>296.4</v>
+        <v>276.67</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I2" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J2" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1413</v>
+      </c>
+      <c r="L2" t="n">
+        <v>110</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.678</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:20.738</t>
+          <t>2026-05-29 09:34:23.680</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1779421642675</v>
+        <v>1780022062376</v>
       </c>
       <c r="C3" t="n">
-        <v>89424</v>
+        <v>83481</v>
       </c>
       <c r="D3" t="n">
-        <v>225.83</v>
+        <v>636.87</v>
       </c>
       <c r="E3" t="n">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="F3" t="n">
-        <v>1631</v>
+        <v>1220</v>
       </c>
       <c r="G3" t="n">
-        <v>296.4</v>
+        <v>276.67</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I3" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J3" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1302</v>
+      </c>
+      <c r="L3" t="n">
+        <v>112</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.696</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:20.739</t>
+          <t>2026-05-29 09:34:23.854</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1779421642876</v>
+        <v>1780022062576</v>
       </c>
       <c r="C4" t="n">
-        <v>89378</v>
+        <v>83664</v>
       </c>
       <c r="D4" t="n">
-        <v>168.54</v>
+        <v>788.03</v>
       </c>
       <c r="E4" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="F4" t="n">
-        <v>745</v>
+        <v>1220</v>
       </c>
       <c r="G4" t="n">
-        <v>291.12</v>
+        <v>276.67</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I4" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J4" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1277</v>
+      </c>
+      <c r="L4" t="n">
+        <v>109</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.918</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:21.189</t>
+          <t>2026-05-29 09:34:23.856</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1779421643078</v>
+        <v>1780022062795</v>
       </c>
       <c r="C5" t="n">
-        <v>88960</v>
+        <v>83923</v>
       </c>
       <c r="D5" t="n">
-        <v>-257.89</v>
+        <v>1007.63</v>
       </c>
       <c r="E5" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="F5" t="n">
-        <v>745</v>
+        <v>1220</v>
       </c>
       <c r="G5" t="n">
-        <v>291.12</v>
+        <v>276.67</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I5" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J5" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1059</v>
+      </c>
+      <c r="L5" t="n">
+        <v>113</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:21.207</t>
+          <t>2026-05-29 09:34:23.857</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1779421643279</v>
+        <v>1780022062995</v>
       </c>
       <c r="C6" t="n">
-        <v>89122</v>
+        <v>83839</v>
       </c>
       <c r="D6" t="n">
-        <v>-83</v>
+        <v>873.25</v>
       </c>
       <c r="E6" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="F6" t="n">
-        <v>745</v>
+        <v>1220</v>
       </c>
       <c r="G6" t="n">
-        <v>291.12</v>
+        <v>276.67</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I6" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K6" t="n">
+        <v>861</v>
+      </c>
+      <c r="L6" t="n">
+        <v>111</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.743</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:21.577</t>
+          <t>2026-05-29 09:34:24.376</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1779421643480</v>
+        <v>1780022063195</v>
       </c>
       <c r="C7" t="n">
-        <v>89209</v>
+        <v>83673</v>
       </c>
       <c r="D7" t="n">
-        <v>8.15</v>
+        <v>663.58</v>
       </c>
       <c r="E7" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="F7" t="n">
-        <v>745</v>
+        <v>1220</v>
       </c>
       <c r="G7" t="n">
-        <v>291.12</v>
+        <v>276.67</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I7" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1180</v>
+      </c>
+      <c r="L7" t="n">
+        <v>112</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.167</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:21.577</t>
+          <t>2026-05-29 09:34:24.399</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1779421643682</v>
+        <v>1780022063395</v>
       </c>
       <c r="C8" t="n">
-        <v>89425</v>
+        <v>83613</v>
       </c>
       <c r="D8" t="n">
-        <v>223.75</v>
+        <v>570.4</v>
       </c>
       <c r="E8" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="F8" t="n">
-        <v>725</v>
+        <v>1220</v>
       </c>
       <c r="G8" t="n">
-        <v>292.96</v>
+        <v>276.67</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I8" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1004</v>
+      </c>
+      <c r="L8" t="n">
+        <v>112</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.519</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:21.952</t>
+          <t>2026-05-29 09:34:24.610</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1779421643883</v>
+        <v>1780022063595</v>
       </c>
       <c r="C9" t="n">
-        <v>88971</v>
+        <v>83187</v>
       </c>
       <c r="D9" t="n">
-        <v>-241.44</v>
+        <v>115.88</v>
       </c>
       <c r="E9" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="F9" t="n">
-        <v>725</v>
+        <v>1220</v>
       </c>
       <c r="G9" t="n">
-        <v>292.96</v>
+        <v>276.67</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I9" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1013</v>
+      </c>
+      <c r="L9" t="n">
+        <v>113</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.23</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:21.953</t>
+          <t>2026-05-29 09:34:24.625</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1779421644085</v>
+        <v>1780022063795</v>
       </c>
       <c r="C10" t="n">
-        <v>89061</v>
+        <v>82496</v>
       </c>
       <c r="D10" t="n">
-        <v>-139.37</v>
+        <v>-580.91</v>
       </c>
       <c r="E10" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="F10" t="n">
-        <v>725</v>
+        <v>1220</v>
       </c>
       <c r="G10" t="n">
-        <v>292.96</v>
+        <v>276.67</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I10" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K10" t="n">
+        <v>829</v>
+      </c>
+      <c r="L10" t="n">
+        <v>111</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.982</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:22.465</t>
+          <t>2026-05-29 09:34:25.208</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1779421644286</v>
+        <v>1780022063995</v>
       </c>
       <c r="C11" t="n">
-        <v>89187</v>
+        <v>82532</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.4</v>
+        <v>-515.86</v>
       </c>
       <c r="E11" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="F11" t="n">
-        <v>725</v>
+        <v>1220</v>
       </c>
       <c r="G11" t="n">
-        <v>292.96</v>
+        <v>276.67</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I11" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J11" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1212</v>
+      </c>
+      <c r="L11" t="n">
+        <v>115</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:22.466</t>
+          <t>2026-05-29 09:34:25.209</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1779421644487</v>
+        <v>1780022064195</v>
       </c>
       <c r="C12" t="n">
-        <v>89362</v>
+        <v>82590</v>
       </c>
       <c r="D12" t="n">
-        <v>168.92</v>
+        <v>-432.07</v>
       </c>
       <c r="E12" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="F12" t="n">
-        <v>866</v>
+        <v>1220</v>
       </c>
       <c r="G12" t="n">
-        <v>292.98</v>
+        <v>276.67</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I12" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1013</v>
+      </c>
+      <c r="L12" t="n">
+        <v>111</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.018</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:22.467</t>
+          <t>2026-05-29 09:34:25.829</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1779421644689</v>
+        <v>1780022064395</v>
       </c>
       <c r="C13" t="n">
-        <v>89550</v>
+        <v>82267</v>
       </c>
       <c r="D13" t="n">
-        <v>348.47</v>
+        <v>-733.47</v>
       </c>
       <c r="E13" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="F13" t="n">
-        <v>866</v>
+        <v>1220</v>
       </c>
       <c r="G13" t="n">
-        <v>292.98</v>
+        <v>276.67</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I13" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1433</v>
+      </c>
+      <c r="L13" t="n">
+        <v>111</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.881</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:22.775</t>
+          <t>2026-05-29 09:34:25.830</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1779421644890</v>
+        <v>1780022064595</v>
       </c>
       <c r="C14" t="n">
-        <v>89079</v>
+        <v>82177</v>
       </c>
       <c r="D14" t="n">
-        <v>-139.95</v>
+        <v>-786.79</v>
       </c>
       <c r="E14" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="F14" t="n">
-        <v>866</v>
+        <v>1220</v>
       </c>
       <c r="G14" t="n">
-        <v>292.98</v>
+        <v>276.67</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I14" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J14" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1234</v>
+      </c>
+      <c r="L14" t="n">
+        <v>114</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.8179999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:23.232</t>
+          <t>2026-05-29 09:34:25.831</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1779421645092</v>
+        <v>1780022064795</v>
       </c>
       <c r="C15" t="n">
-        <v>89277</v>
+        <v>81801</v>
       </c>
       <c r="D15" t="n">
-        <v>65.05</v>
+        <v>-1123.45</v>
       </c>
       <c r="E15" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="F15" t="n">
-        <v>866</v>
+        <v>1220</v>
       </c>
       <c r="G15" t="n">
-        <v>292.98</v>
+        <v>276.67</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I15" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1035</v>
+      </c>
+      <c r="L15" t="n">
+        <v>113</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.862</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:23.233</t>
+          <t>2026-05-29 09:34:26.242</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1779421645293</v>
+        <v>1780022064995</v>
       </c>
       <c r="C16" t="n">
-        <v>89495</v>
+        <v>81970</v>
       </c>
       <c r="D16" t="n">
-        <v>279.79</v>
+        <v>-898.28</v>
       </c>
       <c r="E16" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F16" t="n">
-        <v>846</v>
+        <v>1220</v>
       </c>
       <c r="G16" t="n">
-        <v>226.83</v>
+        <v>276.67</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I16" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1247</v>
+      </c>
+      <c r="L16" t="n">
+        <v>115</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:23.628</t>
+          <t>2026-05-29 09:34:26.244</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1779421645494</v>
+        <v>1780022065214</v>
       </c>
       <c r="C17" t="n">
-        <v>89665</v>
+        <v>83115</v>
       </c>
       <c r="D17" t="n">
-        <v>435.8</v>
+        <v>291.63</v>
       </c>
       <c r="E17" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F17" t="n">
-        <v>846</v>
+        <v>1220</v>
       </c>
       <c r="G17" t="n">
-        <v>226.83</v>
+        <v>276.67</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I17" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1029</v>
+      </c>
+      <c r="L17" t="n">
+        <v>111</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.876</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:23.672</t>
+          <t>2026-05-29 09:34:27.548</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1779421645696</v>
+        <v>1780022065414</v>
       </c>
       <c r="C18" t="n">
-        <v>89242</v>
+        <v>83085</v>
       </c>
       <c r="D18" t="n">
-        <v>-8.99</v>
+        <v>247.05</v>
       </c>
       <c r="E18" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F18" t="n">
-        <v>846</v>
+        <v>1220</v>
       </c>
       <c r="G18" t="n">
-        <v>226.83</v>
+        <v>276.67</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I18" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J18" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2134</v>
+      </c>
+      <c r="L18" t="n">
+        <v>108</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.497</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:24.018</t>
+          <t>2026-05-29 09:34:27.550</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1779421645897</v>
+        <v>1780022065614</v>
       </c>
       <c r="C19" t="n">
-        <v>89467</v>
+        <v>82487</v>
       </c>
       <c r="D19" t="n">
-        <v>216.46</v>
+        <v>-363.3</v>
       </c>
       <c r="E19" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F19" t="n">
-        <v>846</v>
+        <v>1220</v>
       </c>
       <c r="G19" t="n">
-        <v>226.83</v>
+        <v>276.67</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I19" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J19" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1935</v>
+      </c>
+      <c r="L19" t="n">
+        <v>113</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.9389999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:24.019</t>
+          <t>2026-05-29 09:34:27.551</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1779421646099</v>
+        <v>1780022065814</v>
       </c>
       <c r="C20" t="n">
-        <v>89640</v>
+        <v>82109</v>
       </c>
       <c r="D20" t="n">
-        <v>378.64</v>
+        <v>-723.14</v>
       </c>
       <c r="E20" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F20" t="n">
-        <v>806</v>
+        <v>1220</v>
       </c>
       <c r="G20" t="n">
-        <v>219.71</v>
+        <v>276.67</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I20" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J20" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1736</v>
+      </c>
+      <c r="L20" t="n">
+        <v>113</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.93</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:24.416</t>
+          <t>2026-05-29 09:34:27.771</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1779421646300</v>
+        <v>1780022066014</v>
       </c>
       <c r="C21" t="n">
-        <v>89852</v>
+        <v>81959</v>
       </c>
       <c r="D21" t="n">
-        <v>571.71</v>
+        <v>-836.98</v>
       </c>
       <c r="E21" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F21" t="n">
-        <v>806</v>
+        <v>1220</v>
       </c>
       <c r="G21" t="n">
-        <v>219.71</v>
+        <v>276.67</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I21" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J21" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1756</v>
+      </c>
+      <c r="L21" t="n">
+        <v>120</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.994</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:24.416</t>
+          <t>2026-05-29 09:34:27.779</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1779421646502</v>
+        <v>1780022066214</v>
       </c>
       <c r="C22" t="n">
-        <v>89446</v>
+        <v>82534</v>
       </c>
       <c r="D22" t="n">
-        <v>137.12</v>
+        <v>-220.13</v>
       </c>
       <c r="E22" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F22" t="n">
-        <v>806</v>
+        <v>1220</v>
       </c>
       <c r="G22" t="n">
-        <v>219.71</v>
+        <v>276.67</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I22" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1565</v>
+      </c>
+      <c r="L22" t="n">
+        <v>110</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.548</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:24.842</t>
+          <t>2026-05-29 09:34:27.780</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1779421646703</v>
+        <v>1780022066414</v>
       </c>
       <c r="C23" t="n">
-        <v>89684</v>
+        <v>82382</v>
       </c>
       <c r="D23" t="n">
-        <v>368.27</v>
+        <v>-361.12</v>
       </c>
       <c r="E23" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F23" t="n">
-        <v>806</v>
+        <v>1220</v>
       </c>
       <c r="G23" t="n">
-        <v>219.71</v>
+        <v>276.67</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I23" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J23" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1365</v>
+      </c>
+      <c r="L23" t="n">
+        <v>112</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.519</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:24.843</t>
+          <t>2026-05-29 09:34:27.788</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1779421646904</v>
+        <v>1780022066614</v>
       </c>
       <c r="C24" t="n">
-        <v>89765</v>
+        <v>82268</v>
       </c>
       <c r="D24" t="n">
-        <v>430.85</v>
+        <v>-457.07</v>
       </c>
       <c r="E24" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F24" t="n">
-        <v>806</v>
+        <v>1220</v>
       </c>
       <c r="G24" t="n">
-        <v>219.71</v>
+        <v>276.67</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I24" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1173</v>
+      </c>
+      <c r="L24" t="n">
+        <v>109</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.098</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:25.276</t>
+          <t>2026-05-29 09:34:28.881</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1779421647106</v>
+        <v>1780022066814</v>
       </c>
       <c r="C25" t="n">
-        <v>89866</v>
+        <v>82122</v>
       </c>
       <c r="D25" t="n">
-        <v>510.31</v>
+        <v>-580.21</v>
       </c>
       <c r="E25" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F25" t="n">
-        <v>825</v>
+        <v>1220</v>
       </c>
       <c r="G25" t="n">
-        <v>212.53</v>
+        <v>276.67</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I25" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2065</v>
+      </c>
+      <c r="L25" t="n">
+        <v>117</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.206</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:25.277</t>
+          <t>2026-05-29 09:34:28.882</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1779421647307</v>
+        <v>1780022067014</v>
       </c>
       <c r="C26" t="n">
-        <v>89454</v>
+        <v>82175</v>
       </c>
       <c r="D26" t="n">
-        <v>72.8</v>
+        <v>-498.2</v>
       </c>
       <c r="E26" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F26" t="n">
-        <v>825</v>
+        <v>1220</v>
       </c>
       <c r="G26" t="n">
-        <v>212.53</v>
+        <v>276.67</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I26" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J26" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1867</v>
+      </c>
+      <c r="L26" t="n">
+        <v>112</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.174</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:25.277</t>
+          <t>2026-05-29 09:34:28.884</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1779421647509</v>
+        <v>1780022067215</v>
       </c>
       <c r="C27" t="n">
-        <v>89582</v>
+        <v>81726</v>
       </c>
       <c r="D27" t="n">
-        <v>197.16</v>
+        <v>-922.29</v>
       </c>
       <c r="E27" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F27" t="n">
-        <v>825</v>
+        <v>7217</v>
       </c>
       <c r="G27" t="n">
-        <v>212.53</v>
+        <v>276.67</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I27" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J27" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1667</v>
+      </c>
+      <c r="L27" t="n">
+        <v>109</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.403</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:25.677</t>
+          <t>2026-05-29 09:34:28.896</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1779421647710</v>
+        <v>1780022067414</v>
       </c>
       <c r="C28" t="n">
-        <v>89613</v>
+        <v>80270</v>
       </c>
       <c r="D28" t="n">
-        <v>218.3</v>
+        <v>-2332.18</v>
       </c>
       <c r="E28" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F28" t="n">
-        <v>825</v>
+        <v>7217</v>
       </c>
       <c r="G28" t="n">
-        <v>212.53</v>
+        <v>276.67</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I28" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J28" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1480</v>
+      </c>
+      <c r="L28" t="n">
+        <v>112</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.221</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:25.678</t>
+          <t>2026-05-29 09:34:28.966</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1779421647911</v>
+        <v>1780022067614</v>
       </c>
       <c r="C29" t="n">
-        <v>89996</v>
+        <v>80316</v>
       </c>
       <c r="D29" t="n">
-        <v>590.38</v>
+        <v>-2169.57</v>
       </c>
       <c r="E29" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F29" t="n">
-        <v>967</v>
+        <v>7217</v>
       </c>
       <c r="G29" t="n">
-        <v>184.63</v>
+        <v>276.67</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I29" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J29" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1351</v>
+      </c>
+      <c r="L29" t="n">
+        <v>113</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.64</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:26.058</t>
+          <t>2026-05-29 09:34:29.159</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1779421648113</v>
+        <v>1780022067833</v>
       </c>
       <c r="C30" t="n">
-        <v>89424</v>
+        <v>80188</v>
       </c>
       <c r="D30" t="n">
-        <v>-11.14</v>
+        <v>-2189.09</v>
       </c>
       <c r="E30" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F30" t="n">
-        <v>967</v>
+        <v>7217</v>
       </c>
       <c r="G30" t="n">
-        <v>184.63</v>
+        <v>276.67</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I30" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J30" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1325</v>
+      </c>
+      <c r="L30" t="n">
+        <v>110</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.286</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:26.058</t>
+          <t>2026-05-29 09:34:29.162</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1779421648314</v>
+        <v>1780022068033</v>
       </c>
       <c r="C31" t="n">
-        <v>89640</v>
+        <v>80632</v>
       </c>
       <c r="D31" t="n">
-        <v>205.42</v>
+        <v>-1635.64</v>
       </c>
       <c r="E31" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F31" t="n">
-        <v>967</v>
+        <v>7217</v>
       </c>
       <c r="G31" t="n">
-        <v>184.63</v>
+        <v>276.67</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I31" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J31" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1128</v>
+      </c>
+      <c r="L31" t="n">
+        <v>99</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.318</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:26.481</t>
+          <t>2026-05-29 09:34:29.395</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1779421648516</v>
+        <v>1780022068233</v>
       </c>
       <c r="C32" t="n">
-        <v>89793</v>
+        <v>81234</v>
       </c>
       <c r="D32" t="n">
-        <v>348.15</v>
+        <v>-951.86</v>
       </c>
       <c r="E32" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F32" t="n">
-        <v>967</v>
+        <v>7217</v>
       </c>
       <c r="G32" t="n">
-        <v>184.63</v>
+        <v>276.67</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I32" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J32" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1161</v>
+      </c>
+      <c r="L32" t="n">
+        <v>109</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.112</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:26.481</t>
+          <t>2026-05-29 09:34:29.416</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1779421648717</v>
+        <v>1780022068433</v>
       </c>
       <c r="C33" t="n">
-        <v>89931</v>
+        <v>81873</v>
       </c>
       <c r="D33" t="n">
-        <v>468.74</v>
+        <v>-265.26</v>
       </c>
       <c r="E33" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F33" t="n">
-        <v>685</v>
+        <v>7217</v>
       </c>
       <c r="G33" t="n">
-        <v>101.38</v>
+        <v>276.67</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I33" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J33" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K33" t="n">
+        <v>981</v>
+      </c>
+      <c r="L33" t="n">
+        <v>115</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:26.866</t>
+          <t>2026-05-29 09:34:31.460</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1779421648918</v>
+        <v>1780022068633</v>
       </c>
       <c r="C34" t="n">
-        <v>89567</v>
+        <v>82877</v>
       </c>
       <c r="D34" t="n">
-        <v>81.31</v>
+        <v>752</v>
       </c>
       <c r="E34" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F34" t="n">
-        <v>685</v>
+        <v>7217</v>
       </c>
       <c r="G34" t="n">
-        <v>101.38</v>
+        <v>276.67</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I34" t="n">
+        <v>49.26</v>
+      </c>
+      <c r="J34" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2826</v>
+      </c>
+      <c r="L34" t="n">
+        <v>109</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.977</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:26.867</t>
+          <t>2026-05-29 09:34:31.462</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1779421649120</v>
+        <v>1780022068833</v>
       </c>
       <c r="C35" t="n">
-        <v>89743</v>
+        <v>83206</v>
       </c>
       <c r="D35" t="n">
-        <v>253.24</v>
+        <v>1043.4</v>
       </c>
       <c r="E35" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="F35" t="n">
-        <v>685</v>
+        <v>7217</v>
       </c>
       <c r="G35" t="n">
-        <v>101.38</v>
+        <v>276.67</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I35" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J35" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2627</v>
+      </c>
+      <c r="L35" t="n">
+        <v>118</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.362</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:27.300</t>
+          <t>2026-05-29 09:34:31.463</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1779421649321</v>
+        <v>1780022069033</v>
       </c>
       <c r="C36" t="n">
-        <v>89951</v>
+        <v>82554</v>
       </c>
       <c r="D36" t="n">
-        <v>448.58</v>
+        <v>339.23</v>
       </c>
       <c r="E36" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="F36" t="n">
-        <v>685</v>
+        <v>7217</v>
       </c>
       <c r="G36" t="n">
-        <v>103.11</v>
+        <v>276.67</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I36" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J36" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2429</v>
+      </c>
+      <c r="L36" t="n">
+        <v>109</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.26</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:27.301</t>
+          <t>2026-05-29 09:34:31.466</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1779421649523</v>
+        <v>1780022069233</v>
       </c>
       <c r="C37" t="n">
-        <v>89388</v>
+        <v>82232</v>
       </c>
       <c r="D37" t="n">
-        <v>-136.85</v>
+        <v>0.27</v>
       </c>
       <c r="E37" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="F37" t="n">
-        <v>685</v>
+        <v>7217</v>
       </c>
       <c r="G37" t="n">
-        <v>103.11</v>
+        <v>276.67</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I37" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J37" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2231</v>
+      </c>
+      <c r="L37" t="n">
+        <v>121</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.798</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:27.808</t>
+          <t>2026-05-29 09:34:31.468</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1779421649724</v>
+        <v>1780022069433</v>
       </c>
       <c r="C38" t="n">
-        <v>89599</v>
+        <v>82601</v>
       </c>
       <c r="D38" t="n">
-        <v>80.98999999999999</v>
+        <v>369.26</v>
       </c>
       <c r="E38" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="F38" t="n">
-        <v>685</v>
+        <v>7217</v>
       </c>
       <c r="G38" t="n">
-        <v>103.11</v>
+        <v>276.67</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I38" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J38" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2033</v>
+      </c>
+      <c r="L38" t="n">
+        <v>105</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.629</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:27.809</t>
+          <t>2026-05-29 09:34:31.469</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1779421649925</v>
+        <v>1780022069633</v>
       </c>
       <c r="C39" t="n">
-        <v>89661</v>
+        <v>83794</v>
       </c>
       <c r="D39" t="n">
-        <v>138.94</v>
+        <v>1543.79</v>
       </c>
       <c r="E39" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="F39" t="n">
-        <v>685</v>
+        <v>7217</v>
       </c>
       <c r="G39" t="n">
-        <v>103.11</v>
+        <v>276.67</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I39" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J39" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K39" t="n">
+        <v>1835</v>
+      </c>
+      <c r="L39" t="n">
+        <v>110</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.183</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:28.135</t>
+          <t>2026-05-29 09:34:31.471</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1779421650127</v>
+        <v>1780022069833</v>
       </c>
       <c r="C40" t="n">
-        <v>89822</v>
+        <v>84528</v>
       </c>
       <c r="D40" t="n">
-        <v>292.99</v>
+        <v>2200.6</v>
       </c>
       <c r="E40" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="F40" t="n">
-        <v>846</v>
+        <v>7217</v>
       </c>
       <c r="G40" t="n">
-        <v>89.59</v>
+        <v>276.67</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I40" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J40" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1637</v>
+      </c>
+      <c r="L40" t="n">
+        <v>112</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.299</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:28.136</t>
+          <t>2026-05-29 09:34:31.472</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1779421650328</v>
+        <v>1780022070033</v>
       </c>
       <c r="C41" t="n">
-        <v>89196</v>
+        <v>84655</v>
       </c>
       <c r="D41" t="n">
-        <v>-347.65</v>
+        <v>2217.57</v>
       </c>
       <c r="E41" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="F41" t="n">
-        <v>846</v>
+        <v>7217</v>
       </c>
       <c r="G41" t="n">
-        <v>89.59</v>
+        <v>276.67</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I41" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J41" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1438</v>
+      </c>
+      <c r="L41" t="n">
+        <v>107</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.242</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:28.509</t>
+          <t>2026-05-29 09:34:32.360</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1779421650530</v>
+        <v>1780022070252</v>
       </c>
       <c r="C42" t="n">
-        <v>89388</v>
+        <v>84359</v>
       </c>
       <c r="D42" t="n">
-        <v>-138.27</v>
+        <v>1810.69</v>
       </c>
       <c r="E42" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="F42" t="n">
-        <v>846</v>
+        <v>7217</v>
       </c>
       <c r="G42" t="n">
-        <v>89.59</v>
+        <v>276.67</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I42" t="n">
+        <v>49.27</v>
+      </c>
+      <c r="J42" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2107</v>
+      </c>
+      <c r="L42" t="n">
+        <v>113</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.088</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:28.525</t>
+          <t>2026-05-29 09:34:32.362</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1779421650731</v>
+        <v>1780022070452</v>
       </c>
       <c r="C43" t="n">
-        <v>89501</v>
+        <v>84375</v>
       </c>
       <c r="D43" t="n">
-        <v>-18.36</v>
+        <v>1736.16</v>
       </c>
       <c r="E43" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="F43" t="n">
-        <v>846</v>
+        <v>7217</v>
       </c>
       <c r="G43" t="n">
-        <v>89.59</v>
+        <v>276.67</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I43" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J43" t="n">
+        <v>35.46</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1908</v>
+      </c>
+      <c r="L43" t="n">
+        <v>101</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.445</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:28.922</t>
+          <t>2026-05-29 09:34:32.375</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1779421650932</v>
+        <v>1780022070772</v>
       </c>
       <c r="C44" t="n">
-        <v>89547</v>
+        <v>85070</v>
       </c>
       <c r="D44" t="n">
-        <v>28.56</v>
+        <v>2344.35</v>
       </c>
       <c r="E44" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="F44" t="n">
-        <v>765</v>
+        <v>7217</v>
       </c>
       <c r="G44" t="n">
-        <v>88.45</v>
+        <v>276.67</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I44" t="n">
+        <v>46.64</v>
+      </c>
+      <c r="J44" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1602</v>
+      </c>
+      <c r="L44" t="n">
+        <v>124</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.912</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:28.923</t>
+          <t>2026-05-29 09:34:32.411</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1779421651134</v>
+        <v>1780022070972</v>
       </c>
       <c r="C45" t="n">
-        <v>89148</v>
+        <v>85239</v>
       </c>
       <c r="D45" t="n">
-        <v>-371.87</v>
+        <v>2396.13</v>
       </c>
       <c r="E45" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="F45" t="n">
-        <v>765</v>
+        <v>7217</v>
       </c>
       <c r="G45" t="n">
-        <v>88.45</v>
+        <v>276.67</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I45" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J45" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1437</v>
+      </c>
+      <c r="L45" t="n">
+        <v>112</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.682</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:29.325</t>
+          <t>2026-05-29 09:34:32.815</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1779421651335</v>
+        <v>1780022071172</v>
       </c>
       <c r="C46" t="n">
-        <v>89462</v>
+        <v>85526</v>
       </c>
       <c r="D46" t="n">
-        <v>-39.28</v>
+        <v>2563.33</v>
       </c>
       <c r="E46" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="F46" t="n">
-        <v>765</v>
+        <v>7217</v>
       </c>
       <c r="G46" t="n">
-        <v>88.45</v>
+        <v>276.67</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I46" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J46" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1641</v>
+      </c>
+      <c r="L46" t="n">
+        <v>115</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.905</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:29.325</t>
+          <t>2026-05-29 09:34:32.836</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1779421651537</v>
+        <v>1780022071372</v>
       </c>
       <c r="C47" t="n">
-        <v>89628</v>
+        <v>85364</v>
       </c>
       <c r="D47" t="n">
-        <v>128.69</v>
+        <v>2273.16</v>
       </c>
       <c r="E47" t="n">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="F47" t="n">
-        <v>584</v>
+        <v>7217</v>
       </c>
       <c r="G47" t="n">
-        <v>110.51</v>
+        <v>276.67</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I47" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J47" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1463</v>
+      </c>
+      <c r="L47" t="n">
+        <v>109</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.195</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:29.781</t>
+          <t>2026-05-29 09:34:32.837</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1779421651738</v>
+        <v>1780022071572</v>
       </c>
       <c r="C48" t="n">
-        <v>89108</v>
+        <v>84792</v>
       </c>
       <c r="D48" t="n">
-        <v>-397.75</v>
+        <v>1587.5</v>
       </c>
       <c r="E48" t="n">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="F48" t="n">
-        <v>584</v>
+        <v>7217</v>
       </c>
       <c r="G48" t="n">
-        <v>110.51</v>
+        <v>276.67</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I48" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J48" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1264</v>
+      </c>
+      <c r="L48" t="n">
+        <v>112</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.89</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:29.782</t>
+          <t>2026-05-29 09:34:33.189</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1779421651939</v>
+        <v>1780022071772</v>
       </c>
       <c r="C49" t="n">
-        <v>89309</v>
+        <v>84790</v>
       </c>
       <c r="D49" t="n">
-        <v>-176.86</v>
+        <v>1506.13</v>
       </c>
       <c r="E49" t="n">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="F49" t="n">
-        <v>584</v>
+        <v>7217</v>
       </c>
       <c r="G49" t="n">
-        <v>110.51</v>
+        <v>276.67</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I49" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J49" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1415</v>
+      </c>
+      <c r="L49" t="n">
+        <v>118</v>
+      </c>
+      <c r="M49" t="n">
+        <v>2.109</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:30.146</t>
+          <t>2026-05-29 09:34:33.196</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1779421652141</v>
+        <v>1780022071972</v>
       </c>
       <c r="C50" t="n">
-        <v>89512</v>
+        <v>84585</v>
       </c>
       <c r="D50" t="n">
-        <v>34.98</v>
+        <v>1225.82</v>
       </c>
       <c r="E50" t="n">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="F50" t="n">
-        <v>584</v>
+        <v>7217</v>
       </c>
       <c r="G50" t="n">
-        <v>110.51</v>
+        <v>276.67</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I50" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J50" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1221</v>
+      </c>
+      <c r="L50" t="n">
+        <v>107</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.993</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:30.146</t>
+          <t>2026-05-29 09:34:33.198</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1779421652342</v>
+        <v>1780022072172</v>
       </c>
       <c r="C51" t="n">
-        <v>89598</v>
+        <v>83953</v>
       </c>
       <c r="D51" t="n">
-        <v>119.24</v>
+        <v>532.53</v>
       </c>
       <c r="E51" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="F51" t="n">
-        <v>765</v>
+        <v>7217</v>
       </c>
       <c r="G51" t="n">
-        <v>107.1</v>
+        <v>276.67</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I51" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J51" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1024</v>
+      </c>
+      <c r="L51" t="n">
+        <v>115</v>
+      </c>
+      <c r="M51" t="n">
+        <v>2.026</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:30.623</t>
+          <t>2026-05-29 09:34:33.199</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1779421652544</v>
+        <v>1780022072372</v>
       </c>
       <c r="C52" t="n">
-        <v>88975</v>
+        <v>84136</v>
       </c>
       <c r="D52" t="n">
-        <v>-509.73</v>
+        <v>688.9</v>
       </c>
       <c r="E52" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="F52" t="n">
-        <v>765</v>
+        <v>7217</v>
       </c>
       <c r="G52" t="n">
-        <v>107.1</v>
+        <v>276.67</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I52" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J52" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K52" t="n">
+        <v>826</v>
+      </c>
+      <c r="L52" t="n">
+        <v>109</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1.036</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:30.624</t>
+          <t>2026-05-29 09:34:33.604</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1779421652745</v>
+        <v>1780022072591</v>
       </c>
       <c r="C53" t="n">
-        <v>89205</v>
+        <v>84869</v>
       </c>
       <c r="D53" t="n">
-        <v>-254.24</v>
+        <v>1387.46</v>
       </c>
       <c r="E53" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="F53" t="n">
-        <v>765</v>
+        <v>7217</v>
       </c>
       <c r="G53" t="n">
-        <v>107.1</v>
+        <v>276.67</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I53" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J53" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1011</v>
+      </c>
+      <c r="L53" t="n">
+        <v>116</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1.567</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:30.985</t>
+          <t>2026-05-29 09:34:33.670</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1779421652946</v>
+        <v>1780022072791</v>
       </c>
       <c r="C54" t="n">
-        <v>89445</v>
+        <v>85028</v>
       </c>
       <c r="D54" t="n">
-        <v>-1.53</v>
+        <v>1477.09</v>
       </c>
       <c r="E54" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="F54" t="n">
-        <v>765</v>
+        <v>7217</v>
       </c>
       <c r="G54" t="n">
-        <v>107.1</v>
+        <v>276.67</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I54" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J54" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K54" t="n">
+        <v>878</v>
+      </c>
+      <c r="L54" t="n">
+        <v>112</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.869</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:30.985</t>
+          <t>2026-05-29 09:34:34.127</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1779421653148</v>
+        <v>1780022072991</v>
       </c>
       <c r="C55" t="n">
-        <v>89036</v>
+        <v>84583</v>
       </c>
       <c r="D55" t="n">
-        <v>-410.45</v>
+        <v>958.23</v>
       </c>
       <c r="E55" t="n">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="F55" t="n">
-        <v>766</v>
+        <v>7217</v>
       </c>
       <c r="G55" t="n">
-        <v>104.36</v>
+        <v>276.67</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I55" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J55" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1135</v>
+      </c>
+      <c r="L55" t="n">
+        <v>116</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1.09</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:31.599</t>
+          <t>2026-05-29 09:34:34.128</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1779421653349</v>
+        <v>1780022073191</v>
       </c>
       <c r="C56" t="n">
-        <v>89096</v>
+        <v>83845</v>
       </c>
       <c r="D56" t="n">
-        <v>-329.93</v>
+        <v>172.32</v>
       </c>
       <c r="E56" t="n">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="F56" t="n">
-        <v>766</v>
+        <v>7217</v>
       </c>
       <c r="G56" t="n">
-        <v>104.36</v>
+        <v>276.67</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I56" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J56" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K56" t="n">
+        <v>936</v>
+      </c>
+      <c r="L56" t="n">
+        <v>111</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1.104</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:31.600</t>
+          <t>2026-05-29 09:34:34.451</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>1779421653551</v>
+        <v>1780022073391</v>
       </c>
       <c r="C57" t="n">
-        <v>89228</v>
+        <v>83371</v>
       </c>
       <c r="D57" t="n">
-        <v>-181.43</v>
+        <v>-310.3</v>
       </c>
       <c r="E57" t="n">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="F57" t="n">
-        <v>766</v>
+        <v>7217</v>
       </c>
       <c r="G57" t="n">
-        <v>104.36</v>
+        <v>276.67</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I57" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J57" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1058</v>
+      </c>
+      <c r="L57" t="n">
+        <v>118</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1.322</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:31.600</t>
+          <t>2026-05-29 09:34:34.453</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1779421653752</v>
+        <v>1780022073591</v>
       </c>
       <c r="C58" t="n">
-        <v>89438</v>
+        <v>83892</v>
       </c>
       <c r="D58" t="n">
-        <v>37.64</v>
+        <v>226.22</v>
       </c>
       <c r="E58" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="F58" t="n">
-        <v>725</v>
+        <v>7217</v>
       </c>
       <c r="G58" t="n">
-        <v>104.34</v>
+        <v>276.67</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I58" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J58" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K58" t="n">
+        <v>861</v>
+      </c>
+      <c r="L58" t="n">
+        <v>111</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1.368</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:32.021</t>
+          <t>2026-05-29 09:34:35.179</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1779421653953</v>
+        <v>1780022073791</v>
       </c>
       <c r="C59" t="n">
-        <v>88941</v>
+        <v>85257</v>
       </c>
       <c r="D59" t="n">
-        <v>-461.24</v>
+        <v>1579.91</v>
       </c>
       <c r="E59" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="F59" t="n">
-        <v>725</v>
+        <v>7217</v>
       </c>
       <c r="G59" t="n">
-        <v>104.34</v>
+        <v>276.67</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I59" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J59" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1387</v>
+      </c>
+      <c r="L59" t="n">
+        <v>115</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1.15</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:32.022</t>
+          <t>2026-05-29 09:34:35.181</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1779421654155</v>
+        <v>1780022073991</v>
       </c>
       <c r="C60" t="n">
-        <v>89158</v>
+        <v>86479</v>
       </c>
       <c r="D60" t="n">
-        <v>-221.18</v>
+        <v>2722.91</v>
       </c>
       <c r="E60" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="F60" t="n">
-        <v>725</v>
+        <v>7217</v>
       </c>
       <c r="G60" t="n">
-        <v>104.34</v>
+        <v>276.67</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I60" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J60" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K60" t="n">
+        <v>1189</v>
+      </c>
+      <c r="L60" t="n">
+        <v>113</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1.373</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:32.403</t>
+          <t>2026-05-29 09:34:36.175</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1779421654356</v>
+        <v>1780022074191</v>
       </c>
       <c r="C61" t="n">
-        <v>89338</v>
+        <v>79944</v>
       </c>
       <c r="D61" t="n">
-        <v>-30.12</v>
+        <v>-3948.23</v>
       </c>
       <c r="E61" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="F61" t="n">
-        <v>725</v>
+        <v>7217</v>
       </c>
       <c r="G61" t="n">
-        <v>104.34</v>
+        <v>276.67</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I61" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J61" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1983</v>
+      </c>
+      <c r="L61" t="n">
+        <v>118</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.979</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:32.404</t>
+          <t>2026-05-29 09:34:36.207</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1779421654558</v>
+        <v>1780022074391</v>
       </c>
       <c r="C62" t="n">
-        <v>89533</v>
+        <v>80830</v>
       </c>
       <c r="D62" t="n">
-        <v>166.38</v>
+        <v>-2864.82</v>
       </c>
       <c r="E62" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="F62" t="n">
-        <v>705</v>
+        <v>7217</v>
       </c>
       <c r="G62" t="n">
-        <v>103.1</v>
+        <v>276.67</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I62" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J62" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K62" t="n">
+        <v>1814</v>
+      </c>
+      <c r="L62" t="n">
+        <v>110</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1.119</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:32.803</t>
+          <t>2026-05-29 09:34:36.222</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>1779421654759</v>
+        <v>1780022074591</v>
       </c>
       <c r="C63" t="n">
-        <v>88970</v>
+        <v>80512</v>
       </c>
       <c r="D63" t="n">
-        <v>-404.94</v>
+        <v>-3039.58</v>
       </c>
       <c r="E63" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="F63" t="n">
-        <v>705</v>
+        <v>7217</v>
       </c>
       <c r="G63" t="n">
-        <v>103.1</v>
+        <v>276.67</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I63" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J63" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K63" t="n">
+        <v>1630</v>
+      </c>
+      <c r="L63" t="n">
+        <v>108</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1.402</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:32.804</t>
+          <t>2026-05-29 09:34:36.224</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1779421654960</v>
+        <v>1780022074791</v>
       </c>
       <c r="C64" t="n">
-        <v>89229</v>
+        <v>80506</v>
       </c>
       <c r="D64" t="n">
-        <v>-125.69</v>
+        <v>-2893.6</v>
       </c>
       <c r="E64" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="F64" t="n">
-        <v>705</v>
+        <v>7217</v>
       </c>
       <c r="G64" t="n">
-        <v>103.1</v>
+        <v>276.67</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I64" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J64" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K64" t="n">
+        <v>1432</v>
+      </c>
+      <c r="L64" t="n">
+        <v>114</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1.095</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:34.339</t>
+          <t>2026-05-29 09:34:36.226</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1779421655162</v>
+        <v>1780022075010</v>
       </c>
       <c r="C65" t="n">
-        <v>89455</v>
+        <v>80607</v>
       </c>
       <c r="D65" t="n">
-        <v>106.6</v>
+        <v>-2647.92</v>
       </c>
       <c r="E65" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="F65" t="n">
-        <v>725</v>
+        <v>7217</v>
       </c>
       <c r="G65" t="n">
-        <v>69.12</v>
+        <v>276.67</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I65" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J65" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K65" t="n">
+        <v>1215</v>
+      </c>
+      <c r="L65" t="n">
+        <v>112</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1.05</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:34.474</t>
+          <t>2026-05-29 09:34:37.136</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1779421655363</v>
+        <v>1780022075210</v>
       </c>
       <c r="C66" t="n">
-        <v>89442</v>
+        <v>80495</v>
       </c>
       <c r="D66" t="n">
-        <v>88.27</v>
+        <v>-2627.53</v>
       </c>
       <c r="E66" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="F66" t="n">
-        <v>725</v>
+        <v>7217</v>
       </c>
       <c r="G66" t="n">
-        <v>69.12</v>
+        <v>276.67</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I66" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J66" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K66" t="n">
+        <v>1924</v>
+      </c>
+      <c r="L66" t="n">
+        <v>114</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1.428</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:34.475</t>
+          <t>2026-05-29 09:34:37.147</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1779421655565</v>
+        <v>1780022075410</v>
       </c>
       <c r="C67" t="n">
-        <v>89059</v>
+        <v>80629</v>
       </c>
       <c r="D67" t="n">
-        <v>-299.15</v>
+        <v>-2362.15</v>
       </c>
       <c r="E67" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="F67" t="n">
-        <v>725</v>
+        <v>7217</v>
       </c>
       <c r="G67" t="n">
-        <v>69.12</v>
+        <v>276.67</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I67" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J67" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K67" t="n">
+        <v>1736</v>
+      </c>
+      <c r="L67" t="n">
+        <v>115</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.877</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:34.476</t>
+          <t>2026-05-29 09:34:37.323</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1779421655766</v>
+        <v>1780022075610</v>
       </c>
       <c r="C68" t="n">
-        <v>89268</v>
+        <v>79235</v>
       </c>
       <c r="D68" t="n">
-        <v>-75.19</v>
+        <v>-3638.04</v>
       </c>
       <c r="E68" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="F68" t="n">
-        <v>725</v>
+        <v>7217</v>
       </c>
       <c r="G68" t="n">
-        <v>69.12</v>
+        <v>276.67</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I68" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J68" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K68" t="n">
+        <v>1711</v>
+      </c>
+      <c r="L68" t="n">
+        <v>114</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1.68</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:34.476</t>
+          <t>2026-05-29 09:34:37.327</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1779421655967</v>
+        <v>1780022075810</v>
       </c>
       <c r="C69" t="n">
-        <v>89530</v>
+        <v>80210</v>
       </c>
       <c r="D69" t="n">
-        <v>190.57</v>
+        <v>-2481.14</v>
       </c>
       <c r="E69" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="F69" t="n">
-        <v>785</v>
+        <v>7217</v>
       </c>
       <c r="G69" t="n">
-        <v>69.91</v>
+        <v>276.67</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I69" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J69" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1516</v>
+      </c>
+      <c r="L69" t="n">
+        <v>109</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1.182</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:34.477</t>
+          <t>2026-05-29 09:34:37.338</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1779421656169</v>
+        <v>1780022076010</v>
       </c>
       <c r="C70" t="n">
-        <v>89509</v>
+        <v>80852</v>
       </c>
       <c r="D70" t="n">
-        <v>160.04</v>
+        <v>-1715.08</v>
       </c>
       <c r="E70" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="F70" t="n">
-        <v>785</v>
+        <v>7217</v>
       </c>
       <c r="G70" t="n">
-        <v>69.91</v>
+        <v>276.67</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I70" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J70" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K70" t="n">
+        <v>1326</v>
+      </c>
+      <c r="L70" t="n">
+        <v>101</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1.285</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:34.478</t>
+          <t>2026-05-29 09:34:37.353</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1779421656370</v>
+        <v>1780022076210</v>
       </c>
       <c r="C71" t="n">
-        <v>89091</v>
+        <v>81415</v>
       </c>
       <c r="D71" t="n">
-        <v>-265.96</v>
+        <v>-1066.33</v>
       </c>
       <c r="E71" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="F71" t="n">
-        <v>785</v>
+        <v>7217</v>
       </c>
       <c r="G71" t="n">
-        <v>69.91</v>
+        <v>276.67</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I71" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J71" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K71" t="n">
+        <v>1142</v>
+      </c>
+      <c r="L71" t="n">
+        <v>112</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.755</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:34.662</t>
+          <t>2026-05-29 09:34:37.561</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1779421656571</v>
+        <v>1780022076410</v>
       </c>
       <c r="C72" t="n">
-        <v>89210</v>
+        <v>81318</v>
       </c>
       <c r="D72" t="n">
-        <v>-133.66</v>
+        <v>-1110.01</v>
       </c>
       <c r="E72" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="F72" t="n">
-        <v>785</v>
+        <v>7217</v>
       </c>
       <c r="G72" t="n">
-        <v>69.91</v>
+        <v>276.67</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I72" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J72" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1149</v>
+      </c>
+      <c r="L72" t="n">
+        <v>107</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1.521</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:34.662</t>
+          <t>2026-05-29 09:34:37.563</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1779421656773</v>
+        <v>1780022076610</v>
       </c>
       <c r="C73" t="n">
-        <v>89391</v>
+        <v>81707</v>
       </c>
       <c r="D73" t="n">
-        <v>54.02</v>
+        <v>-665.51</v>
       </c>
       <c r="E73" t="n">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="F73" t="n">
-        <v>785</v>
+        <v>7217</v>
       </c>
       <c r="G73" t="n">
-        <v>69.91</v>
+        <v>276.67</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I73" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J73" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K73" t="n">
+        <v>951</v>
+      </c>
+      <c r="L73" t="n">
+        <v>112</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1.184</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:35.063</t>
+          <t>2026-05-29 09:34:38.099</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1779421656974</v>
+        <v>1780022076810</v>
       </c>
       <c r="C74" t="n">
-        <v>88927</v>
+        <v>82462</v>
       </c>
       <c r="D74" t="n">
-        <v>-412.68</v>
+        <v>122.76</v>
       </c>
       <c r="E74" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="F74" t="n">
-        <v>866</v>
+        <v>7217</v>
       </c>
       <c r="G74" t="n">
-        <v>78.41</v>
+        <v>276.67</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I74" t="n">
+        <v>51.72</v>
+      </c>
+      <c r="J74" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K74" t="n">
+        <v>1288</v>
+      </c>
+      <c r="L74" t="n">
+        <v>117</v>
+      </c>
+      <c r="M74" t="n">
+        <v>1.098</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:35.064</t>
+          <t>2026-05-29 09:34:38.132</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1779421657176</v>
+        <v>1780022077029</v>
       </c>
       <c r="C75" t="n">
-        <v>88990</v>
+        <v>82304</v>
       </c>
       <c r="D75" t="n">
-        <v>-329.05</v>
+        <v>-41.37</v>
       </c>
       <c r="E75" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="F75" t="n">
-        <v>866</v>
+        <v>7217</v>
       </c>
       <c r="G75" t="n">
-        <v>78.41</v>
+        <v>276.67</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I75" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J75" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1102</v>
+      </c>
+      <c r="L75" t="n">
+        <v>112</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.191</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:35.466</t>
+          <t>2026-05-29 09:34:38.347</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1779421657377</v>
+        <v>1780022077229</v>
       </c>
       <c r="C76" t="n">
-        <v>89115</v>
+        <v>82438</v>
       </c>
       <c r="D76" t="n">
-        <v>-187.59</v>
+        <v>94.69</v>
       </c>
       <c r="E76" t="n">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="F76" t="n">
-        <v>866</v>
+        <v>7217</v>
       </c>
       <c r="G76" t="n">
-        <v>78.41</v>
+        <v>276.67</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I76" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J76" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K76" t="n">
+        <v>1117</v>
+      </c>
+      <c r="L76" t="n">
+        <v>115</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.961</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:35.467</t>
+          <t>2026-05-29 09:34:38.354</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>1779421657578</v>
+        <v>1780022077429</v>
       </c>
       <c r="C77" t="n">
-        <v>89272</v>
+        <v>82461</v>
       </c>
       <c r="D77" t="n">
-        <v>-21.21</v>
+        <v>112.96</v>
       </c>
       <c r="E77" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="F77" t="n">
-        <v>765</v>
+        <v>7217</v>
       </c>
       <c r="G77" t="n">
-        <v>71.65000000000001</v>
+        <v>276.67</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I77" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J77" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K77" t="n">
+        <v>924</v>
+      </c>
+      <c r="L77" t="n">
+        <v>109</v>
+      </c>
+      <c r="M77" t="n">
+        <v>1.253</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:36.110</t>
+          <t>2026-05-29 09:34:38.725</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1779421657780</v>
+        <v>1780022077629</v>
       </c>
       <c r="C78" t="n">
-        <v>88717</v>
+        <v>82124</v>
       </c>
       <c r="D78" t="n">
-        <v>-575.15</v>
+        <v>-229.69</v>
       </c>
       <c r="E78" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="F78" t="n">
-        <v>765</v>
+        <v>7217</v>
       </c>
       <c r="G78" t="n">
-        <v>71.65000000000001</v>
+        <v>276.67</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I78" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J78" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1095</v>
+      </c>
+      <c r="L78" t="n">
+        <v>120</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1.121</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:36.111</t>
+          <t>2026-05-29 09:34:38.726</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>1779421657981</v>
+        <v>1780022077829</v>
       </c>
       <c r="C79" t="n">
-        <v>88918</v>
+        <v>82325</v>
       </c>
       <c r="D79" t="n">
-        <v>-345.4</v>
+        <v>-17.2</v>
       </c>
       <c r="E79" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="F79" t="n">
-        <v>765</v>
+        <v>7217</v>
       </c>
       <c r="G79" t="n">
-        <v>71.65000000000001</v>
+        <v>276.67</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I79" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J79" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K79" t="n">
+        <v>897</v>
+      </c>
+      <c r="L79" t="n">
+        <v>113</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.727</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:36.112</t>
+          <t>2026-05-29 09:34:40.060</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1779421658183</v>
+        <v>1780022078029</v>
       </c>
       <c r="C80" t="n">
-        <v>89107</v>
+        <v>82165</v>
       </c>
       <c r="D80" t="n">
-        <v>-139.13</v>
+        <v>-176.34</v>
       </c>
       <c r="E80" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="F80" t="n">
-        <v>765</v>
+        <v>7217</v>
       </c>
       <c r="G80" t="n">
-        <v>71.65000000000001</v>
+        <v>276.67</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I80" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J80" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K80" t="n">
+        <v>2030</v>
+      </c>
+      <c r="L80" t="n">
+        <v>115</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1.403</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:36.512</t>
+          <t>2026-05-29 09:34:40.100</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>1779421658384</v>
+        <v>1780022078229</v>
       </c>
       <c r="C81" t="n">
-        <v>89269</v>
+        <v>81629</v>
       </c>
       <c r="D81" t="n">
-        <v>29.83</v>
+        <v>-703.53</v>
       </c>
       <c r="E81" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="F81" t="n">
-        <v>685</v>
+        <v>7217</v>
       </c>
       <c r="G81" t="n">
-        <v>73.62</v>
+        <v>276.67</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I81" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J81" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K81" t="n">
+        <v>1869</v>
+      </c>
+      <c r="L81" t="n">
+        <v>117</v>
+      </c>
+      <c r="M81" t="n">
+        <v>2.116</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:36.512</t>
+          <t>2026-05-29 09:34:40.103</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1779421658585</v>
+        <v>1780022078430</v>
       </c>
       <c r="C82" t="n">
-        <v>88680</v>
+        <v>81427</v>
       </c>
       <c r="D82" t="n">
-        <v>-560.66</v>
+        <v>-870.35</v>
       </c>
       <c r="E82" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="F82" t="n">
-        <v>685</v>
+        <v>7217</v>
       </c>
       <c r="G82" t="n">
-        <v>73.62</v>
+        <v>276.67</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I82" t="n">
+        <v>49.47</v>
+      </c>
+      <c r="J82" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K82" t="n">
+        <v>1671</v>
+      </c>
+      <c r="L82" t="n">
+        <v>121</v>
+      </c>
+      <c r="M82" t="n">
+        <v>2.084</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:36.964</t>
+          <t>2026-05-29 09:34:40.105</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1779421658787</v>
+        <v>1780022078629</v>
       </c>
       <c r="C83" t="n">
-        <v>88762</v>
+        <v>81474</v>
       </c>
       <c r="D83" t="n">
-        <v>-450.63</v>
+        <v>-779.83</v>
       </c>
       <c r="E83" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="F83" t="n">
-        <v>685</v>
+        <v>7217</v>
       </c>
       <c r="G83" t="n">
-        <v>73.62</v>
+        <v>276.67</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I83" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J83" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K83" t="n">
+        <v>1475</v>
+      </c>
+      <c r="L83" t="n">
+        <v>120</v>
+      </c>
+      <c r="M83" t="n">
+        <v>1.311</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:36.965</t>
+          <t>2026-05-29 09:34:40.107</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1779421658988</v>
+        <v>1780022078848</v>
       </c>
       <c r="C84" t="n">
-        <v>88915</v>
+        <v>82773</v>
       </c>
       <c r="D84" t="n">
-        <v>-275.1</v>
+        <v>558.16</v>
       </c>
       <c r="E84" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="F84" t="n">
-        <v>685</v>
+        <v>7217</v>
       </c>
       <c r="G84" t="n">
-        <v>73.62</v>
+        <v>276.67</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I84" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J84" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1258</v>
+      </c>
+      <c r="L84" t="n">
+        <v>107</v>
+      </c>
+      <c r="M84" t="n">
+        <v>1.184</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:36.966</t>
+          <t>2026-05-29 09:34:40.136</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>1779421659190</v>
+        <v>1780022079048</v>
       </c>
       <c r="C85" t="n">
-        <v>89082</v>
+        <v>83146</v>
       </c>
       <c r="D85" t="n">
-        <v>-94.34</v>
+        <v>903.25</v>
       </c>
       <c r="E85" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F85" t="n">
-        <v>906</v>
+        <v>7217</v>
       </c>
       <c r="G85" t="n">
-        <v>69.52</v>
+        <v>276.67</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I85" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J85" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K85" t="n">
+        <v>1087</v>
+      </c>
+      <c r="L85" t="n">
+        <v>109</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1.358</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:37.211</t>
+          <t>2026-05-29 09:34:40.769</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1779421659391</v>
+        <v>1780022079248</v>
       </c>
       <c r="C86" t="n">
-        <v>88552</v>
+        <v>83484</v>
       </c>
       <c r="D86" t="n">
-        <v>-619.63</v>
+        <v>1196.09</v>
       </c>
       <c r="E86" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F86" t="n">
-        <v>906</v>
+        <v>7217</v>
       </c>
       <c r="G86" t="n">
-        <v>69.52</v>
+        <v>276.67</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I86" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J86" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K86" t="n">
+        <v>1520</v>
+      </c>
+      <c r="L86" t="n">
+        <v>112</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0.645</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:37.538</t>
+          <t>2026-05-29 09:34:40.770</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1779421659592</v>
+        <v>1780022079448</v>
       </c>
       <c r="C87" t="n">
-        <v>88750</v>
+        <v>82904</v>
       </c>
       <c r="D87" t="n">
-        <v>-390.64</v>
+        <v>556.28</v>
       </c>
       <c r="E87" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F87" t="n">
-        <v>906</v>
+        <v>7217</v>
       </c>
       <c r="G87" t="n">
-        <v>69.52</v>
+        <v>276.67</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I87" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J87" t="n">
+        <v>35.45</v>
+      </c>
+      <c r="K87" t="n">
+        <v>1321</v>
+      </c>
+      <c r="L87" t="n">
+        <v>119</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0.899</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:37.539</t>
+          <t>2026-05-29 09:34:40.772</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>1779421659794</v>
+        <v>1780022079649</v>
       </c>
       <c r="C88" t="n">
-        <v>88888</v>
+        <v>82951</v>
       </c>
       <c r="D88" t="n">
-        <v>-233.11</v>
+        <v>575.47</v>
       </c>
       <c r="E88" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F88" t="n">
-        <v>906</v>
+        <v>7217</v>
       </c>
       <c r="G88" t="n">
-        <v>69.52</v>
+        <v>276.67</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I88" t="n">
+        <v>49.69</v>
+      </c>
+      <c r="J88" t="n">
+        <v>35.46</v>
+      </c>
+      <c r="K88" t="n">
+        <v>1122</v>
+      </c>
+      <c r="L88" t="n">
+        <v>107</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1.007</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:37.927</t>
+          <t>2026-05-29 09:34:41.192</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1779421659995</v>
+        <v>1780022079848</v>
       </c>
       <c r="C89" t="n">
-        <v>88545</v>
+        <v>82859</v>
       </c>
       <c r="D89" t="n">
-        <v>-564.46</v>
+        <v>454.7</v>
       </c>
       <c r="E89" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="F89" t="n">
-        <v>665</v>
+        <v>7217</v>
       </c>
       <c r="G89" t="n">
-        <v>77</v>
+        <v>276.67</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I89" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J89" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K89" t="n">
+        <v>1343</v>
+      </c>
+      <c r="L89" t="n">
+        <v>118</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1.228</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:37.927</t>
+          <t>2026-05-29 09:34:41.203</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>1779421660197</v>
+        <v>1780022080048</v>
       </c>
       <c r="C90" t="n">
-        <v>88606</v>
+        <v>83191</v>
       </c>
       <c r="D90" t="n">
-        <v>-475.23</v>
+        <v>763.96</v>
       </c>
       <c r="E90" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="F90" t="n">
-        <v>665</v>
+        <v>7217</v>
       </c>
       <c r="G90" t="n">
-        <v>77</v>
+        <v>276.67</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I90" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J90" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1154</v>
+      </c>
+      <c r="L90" t="n">
+        <v>98</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1.005</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:38.364</t>
+          <t>2026-05-29 09:34:41.204</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>1779421660398</v>
+        <v>1780022080248</v>
       </c>
       <c r="C91" t="n">
-        <v>88825</v>
+        <v>82702</v>
       </c>
       <c r="D91" t="n">
-        <v>-232.47</v>
+        <v>236.76</v>
       </c>
       <c r="E91" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="F91" t="n">
-        <v>665</v>
+        <v>7217</v>
       </c>
       <c r="G91" t="n">
-        <v>77</v>
+        <v>276.67</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I91" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J91" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K91" t="n">
+        <v>956</v>
+      </c>
+      <c r="L91" t="n">
+        <v>113</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.605</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:38.365</t>
+          <t>2026-05-29 09:34:42.190</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1779421660599</v>
+        <v>1780022080448</v>
       </c>
       <c r="C92" t="n">
-        <v>88992</v>
+        <v>82615</v>
       </c>
       <c r="D92" t="n">
-        <v>-53.85</v>
+        <v>137.93</v>
       </c>
       <c r="E92" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="F92" t="n">
-        <v>685</v>
+        <v>7217</v>
       </c>
       <c r="G92" t="n">
-        <v>80.40000000000001</v>
+        <v>276.67</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I92" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J92" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K92" t="n">
+        <v>1741</v>
+      </c>
+      <c r="L92" t="n">
+        <v>114</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0.908</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:38.894</t>
+          <t>2026-05-29 09:34:42.191</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>1779421660801</v>
+        <v>1780022080648</v>
       </c>
       <c r="C93" t="n">
-        <v>88471</v>
+        <v>82431</v>
       </c>
       <c r="D93" t="n">
-        <v>-572.16</v>
+        <v>-52.97</v>
       </c>
       <c r="E93" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="F93" t="n">
-        <v>685</v>
+        <v>7217</v>
       </c>
       <c r="G93" t="n">
-        <v>80.40000000000001</v>
+        <v>276.67</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I93" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J93" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K93" t="n">
+        <v>1542</v>
+      </c>
+      <c r="L93" t="n">
+        <v>108</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0.577</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:38.895</t>
+          <t>2026-05-29 09:34:42.717</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>1779421661002</v>
+        <v>1780022080867</v>
       </c>
       <c r="C94" t="n">
-        <v>88870</v>
+        <v>82140</v>
       </c>
       <c r="D94" t="n">
-        <v>-144.55</v>
+        <v>-341.32</v>
       </c>
       <c r="E94" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="F94" t="n">
-        <v>685</v>
+        <v>7217</v>
       </c>
       <c r="G94" t="n">
-        <v>80.40000000000001</v>
+        <v>276.67</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I94" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J94" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K94" t="n">
+        <v>1849</v>
+      </c>
+      <c r="L94" t="n">
+        <v>113</v>
+      </c>
+      <c r="M94" t="n">
+        <v>1.649</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:39.190</t>
+          <t>2026-05-29 09:34:42.719</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>1779421661204</v>
+        <v>1780022081067</v>
       </c>
       <c r="C95" t="n">
-        <v>89182</v>
+        <v>82150</v>
       </c>
       <c r="D95" t="n">
-        <v>174.68</v>
+        <v>-314.26</v>
       </c>
       <c r="E95" t="n">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="F95" t="n">
-        <v>664</v>
+        <v>7217</v>
       </c>
       <c r="G95" t="n">
-        <v>84.8</v>
+        <v>276.67</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I95" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J95" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K95" t="n">
+        <v>1651</v>
+      </c>
+      <c r="L95" t="n">
+        <v>107</v>
+      </c>
+      <c r="M95" t="n">
+        <v>1.301</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:39.214</t>
+          <t>2026-05-29 09:34:42.721</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1779421661405</v>
+        <v>1780022081267</v>
       </c>
       <c r="C96" t="n">
-        <v>89210</v>
+        <v>82146</v>
       </c>
       <c r="D96" t="n">
-        <v>193.95</v>
+        <v>-302.54</v>
       </c>
       <c r="E96" t="n">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="F96" t="n">
-        <v>664</v>
+        <v>7217</v>
       </c>
       <c r="G96" t="n">
-        <v>84.8</v>
+        <v>276.67</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I96" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J96" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1453</v>
+      </c>
+      <c r="L96" t="n">
+        <v>111</v>
+      </c>
+      <c r="M96" t="n">
+        <v>1.167</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:39.590</t>
+          <t>2026-05-29 09:34:42.723</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>1779421661606</v>
+        <v>1780022081467</v>
       </c>
       <c r="C97" t="n">
-        <v>88630</v>
+        <v>82168</v>
       </c>
       <c r="D97" t="n">
-        <v>-395.75</v>
+        <v>-265.42</v>
       </c>
       <c r="E97" t="n">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="F97" t="n">
-        <v>664</v>
+        <v>7217</v>
       </c>
       <c r="G97" t="n">
-        <v>84.8</v>
+        <v>276.67</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I97" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J97" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1254</v>
+      </c>
+      <c r="L97" t="n">
+        <v>106</v>
+      </c>
+      <c r="M97" t="n">
+        <v>1.565</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:39.595</t>
+          <t>2026-05-29 09:34:45.489</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>1779421661808</v>
+        <v>1780022081667</v>
       </c>
       <c r="C98" t="n">
-        <v>88759</v>
+        <v>82906</v>
       </c>
       <c r="D98" t="n">
-        <v>-246.96</v>
+        <v>485.85</v>
       </c>
       <c r="E98" t="n">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="F98" t="n">
-        <v>664</v>
+        <v>14353</v>
       </c>
       <c r="G98" t="n">
-        <v>84.8</v>
+        <v>276.67</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I98" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J98" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K98" t="n">
+        <v>3821</v>
+      </c>
+      <c r="L98" t="n">
+        <v>111</v>
+      </c>
+      <c r="M98" t="n">
+        <v>1.424</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:39.985</t>
+          <t>2026-05-29 09:34:45.491</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1779421662009</v>
+        <v>1780022081867</v>
       </c>
       <c r="C99" t="n">
-        <v>88913</v>
+        <v>83527</v>
       </c>
       <c r="D99" t="n">
-        <v>-80.62</v>
+        <v>1082.56</v>
       </c>
       <c r="E99" t="n">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="F99" t="n">
-        <v>664</v>
+        <v>14353</v>
       </c>
       <c r="G99" t="n">
-        <v>84.8</v>
+        <v>276.67</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I99" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J99" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K99" t="n">
+        <v>3623</v>
+      </c>
+      <c r="L99" t="n">
+        <v>119</v>
+      </c>
+      <c r="M99" t="n">
+        <v>1.067</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:39.986</t>
+          <t>2026-05-29 09:34:45.494</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1779421662211</v>
+        <v>1780022082067</v>
       </c>
       <c r="C100" t="n">
-        <v>88548</v>
+        <v>83879</v>
       </c>
       <c r="D100" t="n">
-        <v>-441.59</v>
+        <v>1380.43</v>
       </c>
       <c r="E100" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="F100" t="n">
-        <v>947</v>
+        <v>14353</v>
       </c>
       <c r="G100" t="n">
-        <v>104.36</v>
+        <v>276.67</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I100" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J100" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K100" t="n">
+        <v>3425</v>
+      </c>
+      <c r="L100" t="n">
+        <v>120</v>
+      </c>
+      <c r="M100" t="n">
+        <v>2.014</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:40.381</t>
+          <t>2026-05-29 09:34:45.496</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>1779421662412</v>
+        <v>1780022082267</v>
       </c>
       <c r="C101" t="n">
-        <v>88447</v>
+        <v>84922</v>
       </c>
       <c r="D101" t="n">
-        <v>-520.51</v>
+        <v>2354.41</v>
       </c>
       <c r="E101" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="F101" t="n">
-        <v>947</v>
+        <v>14353</v>
       </c>
       <c r="G101" t="n">
-        <v>104.36</v>
+        <v>276.67</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I101" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J101" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K101" t="n">
+        <v>3228</v>
+      </c>
+      <c r="L101" t="n">
+        <v>112</v>
+      </c>
+      <c r="M101" t="n">
+        <v>1.054</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:40.382</t>
+          <t>2026-05-29 09:34:45.544</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1779421662613</v>
+        <v>1780022082467</v>
       </c>
       <c r="C102" t="n">
-        <v>88601</v>
+        <v>84660</v>
       </c>
       <c r="D102" t="n">
-        <v>-340.48</v>
+        <v>1974.69</v>
       </c>
       <c r="E102" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="F102" t="n">
-        <v>947</v>
+        <v>14353</v>
       </c>
       <c r="G102" t="n">
-        <v>104.36</v>
+        <v>276.67</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I102" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J102" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K102" t="n">
+        <v>3075</v>
+      </c>
+      <c r="L102" t="n">
+        <v>119</v>
+      </c>
+      <c r="M102" t="n">
+        <v>1.928</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:40.878</t>
+          <t>2026-05-29 09:34:45.574</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1779421662815</v>
+        <v>1780022082686</v>
       </c>
       <c r="C103" t="n">
-        <v>88803</v>
+        <v>84798</v>
       </c>
       <c r="D103" t="n">
-        <v>-121.46</v>
+        <v>2013.96</v>
       </c>
       <c r="E103" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="F103" t="n">
-        <v>947</v>
+        <v>14353</v>
       </c>
       <c r="G103" t="n">
-        <v>104.36</v>
+        <v>276.67</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I103" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J103" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K103" t="n">
+        <v>2888</v>
+      </c>
+      <c r="L103" t="n">
+        <v>112</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0.798</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:40.878</t>
+          <t>2026-05-29 09:34:45.576</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1779421663016</v>
+        <v>1780022082886</v>
       </c>
       <c r="C104" t="n">
-        <v>88362</v>
+        <v>85024</v>
       </c>
       <c r="D104" t="n">
-        <v>-556.38</v>
+        <v>2139.26</v>
       </c>
       <c r="E104" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="F104" t="n">
-        <v>725</v>
+        <v>14353</v>
       </c>
       <c r="G104" t="n">
-        <v>104.36</v>
+        <v>276.67</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I104" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J104" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K104" t="n">
+        <v>2689</v>
+      </c>
+      <c r="L104" t="n">
+        <v>111</v>
+      </c>
+      <c r="M104" t="n">
+        <v>1.344</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:41.126</t>
+          <t>2026-05-29 09:34:45.578</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1779421663218</v>
+        <v>1780022083086</v>
       </c>
       <c r="C105" t="n">
-        <v>88613</v>
+        <v>85366</v>
       </c>
       <c r="D105" t="n">
-        <v>-277.56</v>
+        <v>2374.3</v>
       </c>
       <c r="E105" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="F105" t="n">
-        <v>725</v>
+        <v>14353</v>
       </c>
       <c r="G105" t="n">
-        <v>104.36</v>
+        <v>276.67</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I105" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J105" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K105" t="n">
+        <v>2491</v>
+      </c>
+      <c r="L105" t="n">
+        <v>115</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0.629</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:41.406</t>
+          <t>2026-05-29 09:34:45.850</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1779421663419</v>
+        <v>1780022083286</v>
       </c>
       <c r="C106" t="n">
-        <v>88865</v>
+        <v>85573</v>
       </c>
       <c r="D106" t="n">
-        <v>-11.69</v>
+        <v>2462.58</v>
       </c>
       <c r="E106" t="n">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="F106" t="n">
-        <v>544</v>
+        <v>14353</v>
       </c>
       <c r="G106" t="n">
-        <v>125.93</v>
+        <v>276.67</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I106" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J106" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K106" t="n">
+        <v>2563</v>
+      </c>
+      <c r="L106" t="n">
+        <v>119</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0.649</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:41.406</t>
+          <t>2026-05-29 09:34:46.146</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>1779421663620</v>
+        <v>1780022083486</v>
       </c>
       <c r="C107" t="n">
-        <v>88390</v>
+        <v>85278</v>
       </c>
       <c r="D107" t="n">
-        <v>-486.1</v>
+        <v>2044.45</v>
       </c>
       <c r="E107" t="n">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="F107" t="n">
-        <v>544</v>
+        <v>14353</v>
       </c>
       <c r="G107" t="n">
-        <v>125.93</v>
+        <v>276.67</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I107" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J107" t="n">
+        <v>35.44</v>
+      </c>
+      <c r="K107" t="n">
+        <v>2659</v>
+      </c>
+      <c r="L107" t="n">
+        <v>121</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0.709</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:41.825</t>
+          <t>2026-05-29 09:34:46.175</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>1779421663822</v>
+        <v>1780022085005</v>
       </c>
       <c r="C108" t="n">
-        <v>88531</v>
+        <v>86142</v>
       </c>
       <c r="D108" t="n">
-        <v>-320.8</v>
+        <v>2806.23</v>
       </c>
       <c r="E108" t="n">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="F108" t="n">
-        <v>544</v>
+        <v>14353</v>
       </c>
       <c r="G108" t="n">
-        <v>125.93</v>
+        <v>276.67</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I108" t="n">
+        <v>59.58</v>
+      </c>
+      <c r="J108" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="K108" t="n">
+        <v>1169</v>
+      </c>
+      <c r="L108" t="n">
+        <v>119</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0.8179999999999999</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:41.836</t>
+          <t>2026-05-29 09:34:46.177</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>1779421664023</v>
+        <v>1780022085205</v>
       </c>
       <c r="C109" t="n">
-        <v>88675</v>
+        <v>86640</v>
       </c>
       <c r="D109" t="n">
-        <v>-160.76</v>
+        <v>3163.92</v>
       </c>
       <c r="E109" t="n">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="F109" t="n">
-        <v>544</v>
+        <v>14353</v>
       </c>
       <c r="G109" t="n">
-        <v>125.93</v>
+        <v>276.67</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I109" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J109" t="n">
+        <v>34.95</v>
+      </c>
+      <c r="K109" t="n">
+        <v>971</v>
+      </c>
+      <c r="L109" t="n">
+        <v>124</v>
+      </c>
+      <c r="M109" t="n">
+        <v>1.714</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:42.224</t>
+          <t>2026-05-29 09:34:46.658</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>1779421664225</v>
+        <v>1780022085405</v>
       </c>
       <c r="C110" t="n">
-        <v>88841</v>
+        <v>86264</v>
       </c>
       <c r="D110" t="n">
-        <v>13.28</v>
+        <v>2629.72</v>
       </c>
       <c r="E110" t="n">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="F110" t="n">
-        <v>745</v>
+        <v>14353</v>
       </c>
       <c r="G110" t="n">
-        <v>118.64</v>
+        <v>276.67</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I110" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="J110" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K110" t="n">
+        <v>1252</v>
+      </c>
+      <c r="L110" t="n">
+        <v>124</v>
+      </c>
+      <c r="M110" t="n">
+        <v>1.164</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:42.225</t>
+          <t>2026-05-29 09:34:46.663</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1779421664426</v>
+        <v>1780022085605</v>
       </c>
       <c r="C111" t="n">
-        <v>88270</v>
+        <v>85784</v>
       </c>
       <c r="D111" t="n">
-        <v>-558.38</v>
+        <v>2018.24</v>
       </c>
       <c r="E111" t="n">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="F111" t="n">
-        <v>745</v>
+        <v>14353</v>
       </c>
       <c r="G111" t="n">
-        <v>118.64</v>
+        <v>276.67</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I111" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J111" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K111" t="n">
+        <v>1058</v>
+      </c>
+      <c r="L111" t="n">
+        <v>125</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0.58</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:42.711</t>
+          <t>2026-05-29 09:34:47.093</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1779421664627</v>
+        <v>1780022085806</v>
       </c>
       <c r="C112" t="n">
-        <v>88429</v>
+        <v>86058</v>
       </c>
       <c r="D112" t="n">
-        <v>-371.46</v>
+        <v>2191.32</v>
       </c>
       <c r="E112" t="n">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="F112" t="n">
-        <v>745</v>
+        <v>14353</v>
       </c>
       <c r="G112" t="n">
-        <v>118.64</v>
+        <v>276.67</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I112" t="n">
+        <v>49.44</v>
+      </c>
+      <c r="J112" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K112" t="n">
+        <v>1286</v>
+      </c>
+      <c r="L112" t="n">
+        <v>110</v>
+      </c>
+      <c r="M112" t="n">
+        <v>1.085</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:42.711</t>
+          <t>2026-05-29 09:34:47.100</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1779421664829</v>
+        <v>1780022086005</v>
       </c>
       <c r="C113" t="n">
-        <v>88631</v>
+        <v>83939</v>
       </c>
       <c r="D113" t="n">
-        <v>-150.89</v>
+        <v>-37.24</v>
       </c>
       <c r="E113" t="n">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="F113" t="n">
-        <v>745</v>
+        <v>14353</v>
       </c>
       <c r="G113" t="n">
-        <v>118.64</v>
+        <v>276.67</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I113" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J113" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K113" t="n">
+        <v>1095</v>
+      </c>
+      <c r="L113" t="n">
+        <v>121</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0.758</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:43.048</t>
+          <t>2026-05-29 09:34:47.527</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>1779421665030</v>
+        <v>1780022086206</v>
       </c>
       <c r="C114" t="n">
-        <v>88553</v>
+        <v>84223</v>
       </c>
       <c r="D114" t="n">
-        <v>-221.35</v>
+        <v>248.62</v>
       </c>
       <c r="E114" t="n">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="F114" t="n">
-        <v>765</v>
+        <v>14353</v>
       </c>
       <c r="G114" t="n">
-        <v>118.64</v>
+        <v>276.67</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I114" t="n">
+        <v>49.49</v>
+      </c>
+      <c r="J114" t="n">
+        <v>35.77</v>
+      </c>
+      <c r="K114" t="n">
+        <v>1320</v>
+      </c>
+      <c r="L114" t="n">
+        <v>158</v>
+      </c>
+      <c r="M114" t="n">
+        <v>1.036</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:43.049</t>
+          <t>2026-05-29 09:34:47.531</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1779421665232</v>
+        <v>1780022086405</v>
       </c>
       <c r="C115" t="n">
-        <v>88212</v>
+        <v>84020</v>
       </c>
       <c r="D115" t="n">
-        <v>-551.28</v>
+        <v>33.19</v>
       </c>
       <c r="E115" t="n">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="F115" t="n">
-        <v>765</v>
+        <v>14353</v>
       </c>
       <c r="G115" t="n">
-        <v>118.64</v>
+        <v>276.67</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I115" t="n">
+        <v>49.41</v>
+      </c>
+      <c r="J115" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K115" t="n">
+        <v>1125</v>
+      </c>
+      <c r="L115" t="n">
+        <v>118</v>
+      </c>
+      <c r="M115" t="n">
+        <v>1.228</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:43.262</t>
+          <t>2026-05-29 09:34:47.994</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>1779421665433</v>
+        <v>1780022086625</v>
       </c>
       <c r="C116" t="n">
-        <v>88381</v>
+        <v>83286</v>
       </c>
       <c r="D116" t="n">
-        <v>-354.72</v>
+        <v>-702.47</v>
       </c>
       <c r="E116" t="n">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="F116" t="n">
-        <v>765</v>
+        <v>14353</v>
       </c>
       <c r="G116" t="n">
-        <v>118.64</v>
+        <v>276.67</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I116" t="n">
+        <v>49.49</v>
+      </c>
+      <c r="J116" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K116" t="n">
+        <v>1367</v>
+      </c>
+      <c r="L116" t="n">
+        <v>112</v>
+      </c>
+      <c r="M116" t="n">
+        <v>1.684</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:43.679</t>
+          <t>2026-05-29 09:34:47.997</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>1779421665634</v>
+        <v>1780022086824</v>
       </c>
       <c r="C117" t="n">
-        <v>88625</v>
+        <v>83213</v>
       </c>
       <c r="D117" t="n">
-        <v>-92.98</v>
+        <v>-740.35</v>
       </c>
       <c r="E117" t="n">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="F117" t="n">
-        <v>745</v>
+        <v>14353</v>
       </c>
       <c r="G117" t="n">
-        <v>117.44</v>
+        <v>276.67</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I117" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="J117" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K117" t="n">
+        <v>1171</v>
+      </c>
+      <c r="L117" t="n">
+        <v>124</v>
+      </c>
+      <c r="M117" t="n">
+        <v>1.883</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:43.680</t>
+          <t>2026-05-29 09:34:47.999</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1779421665836</v>
+        <v>1780022087024</v>
       </c>
       <c r="C118" t="n">
-        <v>88167</v>
+        <v>81185</v>
       </c>
       <c r="D118" t="n">
-        <v>-546.33</v>
+        <v>-2731.33</v>
       </c>
       <c r="E118" t="n">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="F118" t="n">
-        <v>745</v>
+        <v>14353</v>
       </c>
       <c r="G118" t="n">
-        <v>117.44</v>
+        <v>276.67</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I118" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J118" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K118" t="n">
+        <v>974</v>
+      </c>
+      <c r="L118" t="n">
+        <v>120</v>
+      </c>
+      <c r="M118" t="n">
+        <v>1.413</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:44.253</t>
+          <t>2026-05-29 09:34:48.000</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>1779421666037</v>
+        <v>1780022087225</v>
       </c>
       <c r="C119" t="n">
-        <v>88443</v>
+        <v>80076</v>
       </c>
       <c r="D119" t="n">
-        <v>-243.01</v>
+        <v>-3703.76</v>
       </c>
       <c r="E119" t="n">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="F119" t="n">
-        <v>745</v>
+        <v>14353</v>
       </c>
       <c r="G119" t="n">
-        <v>117.44</v>
+        <v>276.67</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I119" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J119" t="n">
+        <v>35.02</v>
+      </c>
+      <c r="K119" t="n">
+        <v>775</v>
+      </c>
+      <c r="L119" t="n">
+        <v>123</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.748</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:44.254</t>
+          <t>2026-05-29 09:34:48.865</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>1779421666239</v>
+        <v>1780022087424</v>
       </c>
       <c r="C120" t="n">
-        <v>88668</v>
+        <v>79775</v>
       </c>
       <c r="D120" t="n">
-        <v>-5.86</v>
+        <v>-3819.57</v>
       </c>
       <c r="E120" t="n">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="F120" t="n">
-        <v>605</v>
+        <v>14353</v>
       </c>
       <c r="G120" t="n">
-        <v>108.12</v>
+        <v>276.67</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I120" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="J120" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1440</v>
+      </c>
+      <c r="L120" t="n">
+        <v>123</v>
+      </c>
+      <c r="M120" t="n">
+        <v>1.01</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:44.536</t>
+          <t>2026-05-29 09:34:48.866</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>1779421666440</v>
+        <v>1780022087624</v>
       </c>
       <c r="C121" t="n">
-        <v>88718</v>
+        <v>85477</v>
       </c>
       <c r="D121" t="n">
-        <v>44.43</v>
+        <v>2073.4</v>
       </c>
       <c r="E121" t="n">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="F121" t="n">
-        <v>605</v>
+        <v>14353</v>
       </c>
       <c r="G121" t="n">
-        <v>108.12</v>
+        <v>276.67</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I121" t="n">
+        <v>49.28</v>
+      </c>
+      <c r="J121" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K121" t="n">
+        <v>1241</v>
+      </c>
+      <c r="L121" t="n">
+        <v>103</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.641</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:44.537</t>
+          <t>2026-05-29 09:34:49.170</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>1779421666641</v>
+        <v>1780022087824</v>
       </c>
       <c r="C122" t="n">
-        <v>88333</v>
+        <v>83343</v>
       </c>
       <c r="D122" t="n">
-        <v>-342.79</v>
+        <v>-164.27</v>
       </c>
       <c r="E122" t="n">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="F122" t="n">
-        <v>605</v>
+        <v>14353</v>
       </c>
       <c r="G122" t="n">
-        <v>108.12</v>
+        <v>276.67</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I122" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J122" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K122" t="n">
+        <v>1345</v>
+      </c>
+      <c r="L122" t="n">
+        <v>119</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.789</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:44.910</t>
+          <t>2026-05-29 09:34:49.171</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>1779421666843</v>
+        <v>1780022088024</v>
       </c>
       <c r="C123" t="n">
-        <v>88557</v>
+        <v>82115</v>
       </c>
       <c r="D123" t="n">
-        <v>-101.65</v>
+        <v>-1384.05</v>
       </c>
       <c r="E123" t="n">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="F123" t="n">
-        <v>605</v>
+        <v>14353</v>
       </c>
       <c r="G123" t="n">
-        <v>108.12</v>
+        <v>276.67</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I123" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J123" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K123" t="n">
+        <v>1146</v>
+      </c>
+      <c r="L123" t="n">
+        <v>110</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.786</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:44.911</t>
+          <t>2026-05-29 09:34:49.172</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>1779421667044</v>
+        <v>1780022088224</v>
       </c>
       <c r="C124" t="n">
-        <v>88811</v>
+        <v>80002</v>
       </c>
       <c r="D124" t="n">
-        <v>157.43</v>
+        <v>-3427.85</v>
       </c>
       <c r="E124" t="n">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="F124" t="n">
-        <v>745</v>
+        <v>14353</v>
       </c>
       <c r="G124" t="n">
-        <v>107.46</v>
+        <v>276.67</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I124" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J124" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K124" t="n">
+        <v>947</v>
+      </c>
+      <c r="L124" t="n">
+        <v>115</v>
+      </c>
+      <c r="M124" t="n">
+        <v>1.06</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:45.374</t>
+          <t>2026-05-29 09:34:49.174</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>1779421667246</v>
+        <v>1780022088424</v>
       </c>
       <c r="C125" t="n">
-        <v>88328</v>
+        <v>78402</v>
       </c>
       <c r="D125" t="n">
-        <v>-333.44</v>
+        <v>-4856.46</v>
       </c>
       <c r="E125" t="n">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="F125" t="n">
-        <v>745</v>
+        <v>14353</v>
       </c>
       <c r="G125" t="n">
-        <v>107.46</v>
+        <v>276.67</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I125" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J125" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K125" t="n">
+        <v>748</v>
+      </c>
+      <c r="L125" t="n">
+        <v>112</v>
+      </c>
+      <c r="M125" t="n">
+        <v>1.268</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:45.375</t>
+          <t>2026-05-29 09:34:49.689</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>1779421667447</v>
+        <v>1780022088643</v>
       </c>
       <c r="C126" t="n">
-        <v>88475</v>
+        <v>78159</v>
       </c>
       <c r="D126" t="n">
-        <v>-169.77</v>
+        <v>-4856.63</v>
       </c>
       <c r="E126" t="n">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="F126" t="n">
-        <v>745</v>
+        <v>14353</v>
       </c>
       <c r="G126" t="n">
-        <v>107.46</v>
+        <v>276.67</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I126" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J126" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K126" t="n">
+        <v>1044</v>
+      </c>
+      <c r="L126" t="n">
+        <v>118</v>
+      </c>
+      <c r="M126" t="n">
+        <v>1.555</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:45.707</t>
+          <t>2026-05-29 09:34:50.102</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1779421667648</v>
+        <v>1780022088843</v>
       </c>
       <c r="C127" t="n">
-        <v>88724</v>
+        <v>77662</v>
       </c>
       <c r="D127" t="n">
-        <v>87.72</v>
+        <v>-5110.8</v>
       </c>
       <c r="E127" t="n">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="F127" t="n">
-        <v>745</v>
+        <v>14353</v>
       </c>
       <c r="G127" t="n">
-        <v>107.46</v>
+        <v>276.67</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I127" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J127" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K127" t="n">
+        <v>1258</v>
+      </c>
+      <c r="L127" t="n">
+        <v>123</v>
+      </c>
+      <c r="M127" t="n">
+        <v>1.159</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:45.708</t>
+          <t>2026-05-29 09:34:50.119</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1779421667850</v>
+        <v>1780022089043</v>
       </c>
       <c r="C128" t="n">
-        <v>88918</v>
+        <v>78051</v>
       </c>
       <c r="D128" t="n">
-        <v>277.33</v>
+        <v>-4466.26</v>
       </c>
       <c r="E128" t="n">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="F128" t="n">
-        <v>765</v>
+        <v>14353</v>
       </c>
       <c r="G128" t="n">
-        <v>107.79</v>
+        <v>276.67</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I128" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J128" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K128" t="n">
+        <v>1074</v>
+      </c>
+      <c r="L128" t="n">
+        <v>111</v>
+      </c>
+      <c r="M128" t="n">
+        <v>1.609</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:46.135</t>
+          <t>2026-05-29 09:34:50.414</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1779421668051</v>
+        <v>1780022089243</v>
       </c>
       <c r="C129" t="n">
-        <v>88356</v>
+        <v>78337</v>
       </c>
       <c r="D129" t="n">
-        <v>-298.53</v>
+        <v>-3956.95</v>
       </c>
       <c r="E129" t="n">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="F129" t="n">
-        <v>765</v>
+        <v>14353</v>
       </c>
       <c r="G129" t="n">
-        <v>107.79</v>
+        <v>276.67</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I129" t="n">
+        <v>49.29</v>
+      </c>
+      <c r="J129" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K129" t="n">
+        <v>1170</v>
+      </c>
+      <c r="L129" t="n">
+        <v>122</v>
+      </c>
+      <c r="M129" t="n">
+        <v>1.079</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:46.136</t>
+          <t>2026-05-29 09:34:50.435</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>1779421668253</v>
+        <v>1780022089443</v>
       </c>
       <c r="C130" t="n">
-        <v>88571</v>
+        <v>78886</v>
       </c>
       <c r="D130" t="n">
-        <v>-68.61</v>
+        <v>-3210.1</v>
       </c>
       <c r="E130" t="n">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="F130" t="n">
-        <v>765</v>
+        <v>14353</v>
       </c>
       <c r="G130" t="n">
-        <v>107.79</v>
+        <v>276.67</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I130" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J130" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K130" t="n">
+        <v>991</v>
+      </c>
+      <c r="L130" t="n">
+        <v>116</v>
+      </c>
+      <c r="M130" t="n">
+        <v>1.091</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:46.526</t>
+          <t>2026-05-29 09:34:50.993</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>1779421668454</v>
+        <v>1780022089643</v>
       </c>
       <c r="C131" t="n">
-        <v>88642</v>
+        <v>78802</v>
       </c>
       <c r="D131" t="n">
-        <v>5.82</v>
+        <v>-3133.6</v>
       </c>
       <c r="E131" t="n">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="F131" t="n">
-        <v>765</v>
+        <v>14353</v>
       </c>
       <c r="G131" t="n">
-        <v>107.79</v>
+        <v>276.67</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I131" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="J131" t="n">
+        <v>34.52</v>
+      </c>
+      <c r="K131" t="n">
+        <v>1349</v>
+      </c>
+      <c r="L131" t="n">
+        <v>127</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.699</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:46.526</t>
+          <t>2026-05-29 09:34:50.994</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>1779421668655</v>
+        <v>1780022089843</v>
       </c>
       <c r="C132" t="n">
-        <v>88760</v>
+        <v>78451</v>
       </c>
       <c r="D132" t="n">
-        <v>123.53</v>
+        <v>-3327.92</v>
       </c>
       <c r="E132" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="F132" t="n">
-        <v>826</v>
+        <v>14353</v>
       </c>
       <c r="G132" t="n">
-        <v>109.76</v>
+        <v>276.67</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I132" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J132" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K132" t="n">
+        <v>1150</v>
+      </c>
+      <c r="L132" t="n">
+        <v>119</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.8129999999999999</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:46.937</t>
+          <t>2026-05-29 09:34:51.144</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>1779421668857</v>
+        <v>1780022090043</v>
       </c>
       <c r="C133" t="n">
-        <v>88270</v>
+        <v>78655</v>
       </c>
       <c r="D133" t="n">
-        <v>-372.64</v>
+        <v>-2957.52</v>
       </c>
       <c r="E133" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="F133" t="n">
-        <v>826</v>
+        <v>14353</v>
       </c>
       <c r="G133" t="n">
-        <v>109.76</v>
+        <v>276.67</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I133" t="n">
+        <v>49.31</v>
+      </c>
+      <c r="J133" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K133" t="n">
+        <v>1100</v>
+      </c>
+      <c r="L133" t="n">
+        <v>112</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.746</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:46.938</t>
+          <t>2026-05-29 09:34:51.173</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>1779421669058</v>
+        <v>1780022090243</v>
       </c>
       <c r="C134" t="n">
-        <v>88490</v>
+        <v>78623</v>
       </c>
       <c r="D134" t="n">
-        <v>-134.01</v>
+        <v>-2841.65</v>
       </c>
       <c r="E134" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="F134" t="n">
-        <v>826</v>
+        <v>8676</v>
       </c>
       <c r="G134" t="n">
-        <v>109.76</v>
+        <v>276.67</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I134" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="J134" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K134" t="n">
+        <v>929</v>
+      </c>
+      <c r="L134" t="n">
+        <v>119</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.871</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:47.380</t>
+          <t>2026-05-29 09:34:51.815</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>1779421669260</v>
+        <v>1780022090443</v>
       </c>
       <c r="C135" t="n">
-        <v>88678</v>
+        <v>78193</v>
       </c>
       <c r="D135" t="n">
-        <v>60.69</v>
+        <v>-3129.56</v>
       </c>
       <c r="E135" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="F135" t="n">
-        <v>685</v>
+        <v>8676</v>
       </c>
       <c r="G135" t="n">
-        <v>83.23999999999999</v>
+        <v>276.67</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I135" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J135" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K135" t="n">
+        <v>1371</v>
+      </c>
+      <c r="L135" t="n">
+        <v>114</v>
+      </c>
+      <c r="M135" t="n">
+        <v>1.282</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:47.381</t>
+          <t>2026-05-29 09:34:51.817</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>1779421669461</v>
+        <v>1780022090643</v>
       </c>
       <c r="C136" t="n">
-        <v>88257</v>
+        <v>78642</v>
       </c>
       <c r="D136" t="n">
-        <v>-363.35</v>
+        <v>-2524.09</v>
       </c>
       <c r="E136" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="F136" t="n">
-        <v>685</v>
+        <v>8676</v>
       </c>
       <c r="G136" t="n">
-        <v>83.23999999999999</v>
+        <v>276.67</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I136" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J136" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K136" t="n">
+        <v>1173</v>
+      </c>
+      <c r="L136" t="n">
+        <v>110</v>
+      </c>
+      <c r="M136" t="n">
+        <v>1.253</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:47.773</t>
+          <t>2026-05-29 09:34:52.490</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>1779421669662</v>
+        <v>1780022090862</v>
       </c>
       <c r="C137" t="n">
-        <v>88388</v>
+        <v>79041</v>
       </c>
       <c r="D137" t="n">
-        <v>-214.18</v>
+        <v>-1998.88</v>
       </c>
       <c r="E137" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F137" t="n">
-        <v>685</v>
+        <v>540</v>
       </c>
       <c r="G137" t="n">
-        <v>83.23999999999999</v>
+        <v>288.57</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I137" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J137" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="K137" t="n">
+        <v>1628</v>
+      </c>
+      <c r="L137" t="n">
+        <v>109</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.53</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:47.816</t>
+          <t>2026-05-29 09:34:52.491</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>1779421669864</v>
+        <v>1780022091062</v>
       </c>
       <c r="C138" t="n">
-        <v>88521</v>
+        <v>78823</v>
       </c>
       <c r="D138" t="n">
-        <v>-70.47</v>
+        <v>-2116.94</v>
       </c>
       <c r="E138" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F138" t="n">
-        <v>685</v>
+        <v>540</v>
       </c>
       <c r="G138" t="n">
-        <v>83.23999999999999</v>
+        <v>288.57</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I138" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J138" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K138" t="n">
+        <v>1429</v>
+      </c>
+      <c r="L138" t="n">
+        <v>106</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.599</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:48.211</t>
+          <t>2026-05-29 09:34:52.549</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>1779421670065</v>
+        <v>1780022091262</v>
       </c>
       <c r="C139" t="n">
-        <v>88675</v>
+        <v>79210</v>
       </c>
       <c r="D139" t="n">
-        <v>87.05</v>
+        <v>-1624.09</v>
       </c>
       <c r="E139" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F139" t="n">
-        <v>725</v>
+        <v>540</v>
       </c>
       <c r="G139" t="n">
-        <v>83.23999999999999</v>
+        <v>288.57</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I139" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J139" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K139" t="n">
+        <v>1286</v>
+      </c>
+      <c r="L139" t="n">
+        <v>105</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.966</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:48.211</t>
+          <t>2026-05-29 09:34:52.552</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1779421670267</v>
+        <v>1780022091462</v>
       </c>
       <c r="C140" t="n">
-        <v>88088</v>
+        <v>79283</v>
       </c>
       <c r="D140" t="n">
-        <v>-504.3</v>
+        <v>-1469.89</v>
       </c>
       <c r="E140" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F140" t="n">
-        <v>725</v>
+        <v>540</v>
       </c>
       <c r="G140" t="n">
-        <v>83.23999999999999</v>
+        <v>288.57</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I140" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J140" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K140" t="n">
+        <v>1089</v>
+      </c>
+      <c r="L140" t="n">
+        <v>103</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.534</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:48.471</t>
+          <t>2026-05-29 09:34:53.091</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>1779421670468</v>
+        <v>1780022091662</v>
       </c>
       <c r="C141" t="n">
-        <v>88334</v>
+        <v>79083</v>
       </c>
       <c r="D141" t="n">
-        <v>-233.08</v>
+        <v>-1596.39</v>
       </c>
       <c r="E141" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F141" t="n">
-        <v>725</v>
+        <v>540</v>
       </c>
       <c r="G141" t="n">
-        <v>83.23999999999999</v>
+        <v>288.57</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I141" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J141" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K141" t="n">
+        <v>1428</v>
+      </c>
+      <c r="L141" t="n">
+        <v>107</v>
+      </c>
+      <c r="M141" t="n">
+        <v>1.436</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:48.471</t>
+          <t>2026-05-29 09:34:53.093</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>1779421670669</v>
+        <v>1780022091862</v>
       </c>
       <c r="C142" t="n">
-        <v>88617</v>
+        <v>79010</v>
       </c>
       <c r="D142" t="n">
-        <v>61.57</v>
+        <v>-1589.57</v>
       </c>
       <c r="E142" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F142" t="n">
-        <v>725</v>
+        <v>540</v>
       </c>
       <c r="G142" t="n">
-        <v>83.23999999999999</v>
+        <v>288.57</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I142" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J142" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K142" t="n">
+        <v>1230</v>
+      </c>
+      <c r="L142" t="n">
+        <v>105</v>
+      </c>
+      <c r="M142" t="n">
+        <v>1.008</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:48.797</t>
+          <t>2026-05-29 09:34:53.139</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1779421670871</v>
+        <v>1780022092062</v>
       </c>
       <c r="C143" t="n">
-        <v>88719</v>
+        <v>78839</v>
       </c>
       <c r="D143" t="n">
-        <v>160.49</v>
+        <v>-1681.09</v>
       </c>
       <c r="E143" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F143" t="n">
-        <v>745</v>
+        <v>540</v>
       </c>
       <c r="G143" t="n">
-        <v>57.72</v>
+        <v>288.57</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I143" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J143" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K143" t="n">
+        <v>1077</v>
+      </c>
+      <c r="L143" t="n">
+        <v>104</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.601</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:49.189</t>
+          <t>2026-05-29 09:34:53.560</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>1779421671072</v>
+        <v>1780022092262</v>
       </c>
       <c r="C144" t="n">
-        <v>88228</v>
+        <v>79124</v>
       </c>
       <c r="D144" t="n">
-        <v>-338.53</v>
+        <v>-1312.04</v>
       </c>
       <c r="E144" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F144" t="n">
-        <v>745</v>
+        <v>540</v>
       </c>
       <c r="G144" t="n">
-        <v>57.72</v>
+        <v>288.57</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
+      </c>
+      <c r="I144" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J144" t="n">
+        <v>34.46</v>
+      </c>
+      <c r="K144" t="n">
+        <v>1297</v>
+      </c>
+      <c r="L144" t="n">
+        <v>116</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0.972</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-05-22 10:47:49.189</t>
+          <t>2026-05-29 09:34:53.622</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>1779421671274</v>
+        <v>1780022092462</v>
       </c>
       <c r="C145" t="n">
-        <v>88324</v>
+        <v>80900</v>
       </c>
       <c r="D145" t="n">
-        <v>-225.61</v>
+        <v>529.5599999999999</v>
       </c>
       <c r="E145" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F145" t="n">
-        <v>745</v>
+        <v>1599</v>
       </c>
       <c r="G145" t="n">
-        <v>57.72</v>
+        <v>288.57</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
           <t>Good (100%)</t>
         </is>
       </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:47:49.655</t>
-        </is>
-      </c>
-      <c r="B146" t="n">
-        <v>1779421671475</v>
-      </c>
-      <c r="C146" t="n">
-        <v>88514</v>
-      </c>
-      <c r="D146" t="n">
-        <v>-24.33</v>
-      </c>
-      <c r="E146" t="n">
-        <v>80</v>
-      </c>
-      <c r="F146" t="n">
-        <v>745</v>
-      </c>
-      <c r="G146" t="n">
-        <v>57.72</v>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:47:49.656</t>
-        </is>
-      </c>
-      <c r="B147" t="n">
-        <v>1779421671676</v>
-      </c>
-      <c r="C147" t="n">
-        <v>88084</v>
-      </c>
-      <c r="D147" t="n">
-        <v>-453.11</v>
-      </c>
-      <c r="E147" t="n">
-        <v>80</v>
-      </c>
-      <c r="F147" t="n">
-        <v>826</v>
-      </c>
-      <c r="G147" t="n">
-        <v>64.54000000000001</v>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:47:49.656</t>
-        </is>
-      </c>
-      <c r="B148" t="n">
-        <v>1779421671878</v>
-      </c>
-      <c r="C148" t="n">
-        <v>88332</v>
-      </c>
-      <c r="D148" t="n">
-        <v>-182.45</v>
-      </c>
-      <c r="E148" t="n">
-        <v>80</v>
-      </c>
-      <c r="F148" t="n">
-        <v>826</v>
-      </c>
-      <c r="G148" t="n">
-        <v>64.54000000000001</v>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:47:49.832</t>
-        </is>
-      </c>
-      <c r="B149" t="n">
-        <v>1779421672079</v>
-      </c>
-      <c r="C149" t="n">
-        <v>88542</v>
-      </c>
-      <c r="D149" t="n">
-        <v>36.67</v>
-      </c>
-      <c r="E149" t="n">
-        <v>80</v>
-      </c>
-      <c r="F149" t="n">
-        <v>826</v>
-      </c>
-      <c r="G149" t="n">
-        <v>64.54000000000001</v>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:47:50.299</t>
-        </is>
-      </c>
-      <c r="B150" t="n">
-        <v>1779421672281</v>
-      </c>
-      <c r="C150" t="n">
-        <v>88795</v>
-      </c>
-      <c r="D150" t="n">
-        <v>287.84</v>
-      </c>
-      <c r="E150" t="n">
-        <v>84</v>
-      </c>
-      <c r="F150" t="n">
-        <v>584</v>
-      </c>
-      <c r="G150" t="n">
-        <v>81.02</v>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:47:50.299</t>
-        </is>
-      </c>
-      <c r="B151" t="n">
-        <v>1779421672482</v>
-      </c>
-      <c r="C151" t="n">
-        <v>88241</v>
-      </c>
-      <c r="D151" t="n">
-        <v>-280.56</v>
-      </c>
-      <c r="E151" t="n">
-        <v>84</v>
-      </c>
-      <c r="F151" t="n">
-        <v>584</v>
-      </c>
-      <c r="G151" t="n">
-        <v>81.02</v>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:47:50.643</t>
-        </is>
-      </c>
-      <c r="B152" t="n">
-        <v>1779421672683</v>
-      </c>
-      <c r="C152" t="n">
-        <v>88433</v>
-      </c>
-      <c r="D152" t="n">
-        <v>-74.53</v>
-      </c>
-      <c r="E152" t="n">
-        <v>84</v>
-      </c>
-      <c r="F152" t="n">
-        <v>584</v>
-      </c>
-      <c r="G152" t="n">
-        <v>81.02</v>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:47:50.644</t>
-        </is>
-      </c>
-      <c r="B153" t="n">
-        <v>1779421672885</v>
-      </c>
-      <c r="C153" t="n">
-        <v>88640</v>
-      </c>
-      <c r="D153" t="n">
-        <v>136.2</v>
-      </c>
-      <c r="E153" t="n">
-        <v>84</v>
-      </c>
-      <c r="F153" t="n">
-        <v>584</v>
-      </c>
-      <c r="G153" t="n">
-        <v>81.02</v>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>2026-05-22 10:47:51.046</t>
-        </is>
-      </c>
-      <c r="B154" t="n">
-        <v>1779421673086</v>
-      </c>
-      <c r="C154" t="n">
-        <v>88866</v>
-      </c>
-      <c r="D154" t="n">
-        <v>355.39</v>
-      </c>
-      <c r="E154" t="n">
-        <v>82</v>
-      </c>
-      <c r="F154" t="n">
-        <v>785</v>
-      </c>
-      <c r="G154" t="n">
-        <v>83.08</v>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Good (100%)</t>
-        </is>
+      <c r="I145" t="n">
+        <v>49.32</v>
+      </c>
+      <c r="J145" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="K145" t="n">
+        <v>1159</v>
+      </c>
+      <c r="L145" t="n">
+        <v>112</v>
+      </c>
+      <c r="M145" t="n">
+        <v>0.651</v>
       </c>
     </row>
   </sheetData>
